--- a/Thesis/developer_states.xlsx
+++ b/Thesis/developer_states.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/abigail_weeks_rmi_org/Documents/Documents/GitHub/Thesis/Thesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="235" documentId="8_{A4B64DE1-C1F9-4DF8-A805-E80C52345F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB0A0579-2F43-4F02-A61D-396F018F607F}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="8_{A4B64DE1-C1F9-4DF8-A805-E80C52345F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DB9B39E-0EE8-4C09-A485-2566A200D2DF}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{31558D2F-F994-4500-BC80-1C41F5323AB0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31558D2F-F994-4500-BC80-1C41F5323AB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1843,7 +1843,8 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <f>1/1000</f>
+        <v>1E-3</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>319</v>
@@ -1866,7 +1867,8 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <f t="shared" ref="C3:C66" si="0">1/1000</f>
+        <v>1E-3</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>320</v>
@@ -1889,7 +1891,8 @@
         <v>429</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>321</v>
@@ -1912,7 +1915,8 @@
         <v>429</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>321</v>
@@ -1935,7 +1939,8 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>322</v>
@@ -1958,7 +1963,8 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>323</v>
@@ -1981,7 +1987,8 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>324</v>
@@ -2004,7 +2011,8 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>325</v>
@@ -2027,7 +2035,8 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>326</v>
@@ -2050,7 +2059,8 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>327</v>
@@ -2073,7 +2083,8 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>328</v>
@@ -2096,7 +2107,8 @@
         <v>4</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>329</v>
@@ -2119,7 +2131,8 @@
         <v>6</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>330</v>
@@ -2142,7 +2155,8 @@
         <v>6</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>331</v>
@@ -2165,7 +2179,8 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>332</v>
@@ -2188,7 +2203,8 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>333</v>
@@ -2211,7 +2227,8 @@
         <v>4</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>334</v>
@@ -2234,7 +2251,8 @@
         <v>4</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>335</v>
@@ -2257,7 +2275,8 @@
         <v>4</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>335</v>
@@ -2280,7 +2299,8 @@
         <v>4</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>336</v>
@@ -2303,7 +2323,8 @@
         <v>4</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>332</v>
@@ -2326,7 +2347,8 @@
         <v>4</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>337</v>
@@ -2349,7 +2371,8 @@
         <v>4</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>338</v>
@@ -2372,7 +2395,8 @@
         <v>4</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>339</v>
@@ -2395,7 +2419,8 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>340</v>
@@ -2418,7 +2443,8 @@
         <v>6</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>341</v>
@@ -2441,7 +2467,8 @@
         <v>5</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>340</v>
@@ -2464,7 +2491,8 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>327</v>
@@ -2487,7 +2515,8 @@
         <v>4</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>339</v>
@@ -2510,7 +2539,8 @@
         <v>7</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>342</v>
@@ -2533,7 +2563,8 @@
         <v>4</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>327</v>
@@ -2556,7 +2587,8 @@
         <v>4</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>327</v>
@@ -2579,7 +2611,8 @@
         <v>6</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>343</v>
@@ -2602,7 +2635,8 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>343</v>
@@ -2625,7 +2659,8 @@
         <v>4</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>335</v>
@@ -2648,7 +2683,8 @@
         <v>6</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>344</v>
@@ -2671,7 +2707,8 @@
         <v>7</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>345</v>
@@ -2694,7 +2731,8 @@
         <v>4</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>339</v>
@@ -2717,7 +2755,8 @@
         <v>4</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>332</v>
@@ -2740,7 +2779,8 @@
         <v>4</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>335</v>
@@ -2763,7 +2803,8 @@
         <v>4</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>332</v>
@@ -2786,7 +2827,8 @@
         <v>6</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>340</v>
@@ -2809,7 +2851,8 @@
         <v>7</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>346</v>
@@ -2832,7 +2875,8 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D45" s="3">
         <v>11</v>
@@ -2855,7 +2899,8 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D46" s="3">
         <v>11</v>
@@ -2878,7 +2923,8 @@
         <v>4</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>332</v>
@@ -2901,7 +2947,8 @@
         <v>7</v>
       </c>
       <c r="C48">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>347</v>
@@ -2924,7 +2971,8 @@
         <v>7</v>
       </c>
       <c r="C49">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>348</v>
@@ -2947,7 +2995,8 @@
         <v>6</v>
       </c>
       <c r="C50">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>349</v>
@@ -2970,7 +3019,8 @@
         <v>4</v>
       </c>
       <c r="C51">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>339</v>
@@ -2993,7 +3043,8 @@
         <v>4</v>
       </c>
       <c r="C52">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>335</v>
@@ -3016,7 +3067,8 @@
         <v>4</v>
       </c>
       <c r="C53">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>327</v>
@@ -3039,7 +3091,8 @@
         <v>7</v>
       </c>
       <c r="C54">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>327</v>
@@ -3062,7 +3115,8 @@
         <v>6</v>
       </c>
       <c r="C55">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>343</v>
@@ -3085,7 +3139,8 @@
         <v>4</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>335</v>
@@ -3108,7 +3163,8 @@
         <v>7</v>
       </c>
       <c r="C57">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>335</v>
@@ -3131,7 +3187,8 @@
         <v>6</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>327</v>
@@ -3154,7 +3211,8 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>327</v>
@@ -3177,7 +3235,8 @@
         <v>6</v>
       </c>
       <c r="C60">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>339</v>
@@ -3200,7 +3259,8 @@
         <v>7</v>
       </c>
       <c r="C61">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>327</v>
@@ -3223,7 +3283,8 @@
         <v>7</v>
       </c>
       <c r="C62">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>350</v>
@@ -3246,7 +3307,8 @@
         <v>4</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>351</v>
@@ -3269,7 +3331,8 @@
         <v>7</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>352</v>
@@ -3292,7 +3355,8 @@
         <v>4</v>
       </c>
       <c r="C65">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>332</v>
@@ -3315,7 +3379,8 @@
         <v>4</v>
       </c>
       <c r="C66">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1E-3</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>347</v>
@@ -3338,7 +3403,8 @@
         <v>7</v>
       </c>
       <c r="C67">
-        <v>5</v>
+        <f t="shared" ref="C67:C130" si="1">1/1000</f>
+        <v>1E-3</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>353</v>
@@ -3361,7 +3427,8 @@
         <v>430</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D68" s="3">
         <v>11</v>
@@ -3384,7 +3451,8 @@
         <v>4</v>
       </c>
       <c r="C69">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>335</v>
@@ -3407,7 +3475,8 @@
         <v>4</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>332</v>
@@ -3430,7 +3499,8 @@
         <v>4</v>
       </c>
       <c r="C71">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>354</v>
@@ -3453,7 +3523,8 @@
         <v>4</v>
       </c>
       <c r="C72">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>339</v>
@@ -3476,7 +3547,8 @@
         <v>7</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>339</v>
@@ -3499,7 +3571,8 @@
         <v>4</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>339</v>
@@ -3522,7 +3595,8 @@
         <v>4</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>327</v>
@@ -3545,7 +3619,8 @@
         <v>7</v>
       </c>
       <c r="C76">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>332</v>
@@ -3568,7 +3643,8 @@
         <v>7</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>332</v>
@@ -3591,7 +3667,8 @@
         <v>6</v>
       </c>
       <c r="C78">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D78" s="3">
         <v>200</v>
@@ -3614,7 +3691,8 @@
         <v>4</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>339</v>
@@ -3637,7 +3715,8 @@
         <v>4</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>355</v>
@@ -3660,7 +3739,8 @@
         <v>4</v>
       </c>
       <c r="C81">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>339</v>
@@ -3683,7 +3763,8 @@
         <v>4</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>356</v>
@@ -3706,7 +3787,8 @@
         <v>4</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>357</v>
@@ -3729,7 +3811,8 @@
         <v>4</v>
       </c>
       <c r="C84">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>348</v>
@@ -3752,7 +3835,8 @@
         <v>6</v>
       </c>
       <c r="C85">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>358</v>
@@ -3775,7 +3859,8 @@
         <v>4</v>
       </c>
       <c r="C86">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>359</v>
@@ -3798,7 +3883,8 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>335</v>
@@ -3821,7 +3907,8 @@
         <v>4</v>
       </c>
       <c r="C88">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>355</v>
@@ -3844,7 +3931,8 @@
         <v>6</v>
       </c>
       <c r="C89">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>343</v>
@@ -3867,7 +3955,8 @@
         <v>6</v>
       </c>
       <c r="C90">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>335</v>
@@ -3890,7 +3979,8 @@
         <v>5</v>
       </c>
       <c r="C91">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>360</v>
@@ -3913,7 +4003,8 @@
         <v>4</v>
       </c>
       <c r="C92">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>335</v>
@@ -3936,7 +4027,8 @@
         <v>4</v>
       </c>
       <c r="C93">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>335</v>
@@ -3959,7 +4051,8 @@
         <v>4</v>
       </c>
       <c r="C94">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>335</v>
@@ -3982,7 +4075,8 @@
         <v>4</v>
       </c>
       <c r="C95">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>335</v>
@@ -4005,7 +4099,8 @@
         <v>7</v>
       </c>
       <c r="C96">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>347</v>
@@ -4028,7 +4123,8 @@
         <v>4</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>361</v>
@@ -4051,7 +4147,8 @@
         <v>6</v>
       </c>
       <c r="C98">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>362</v>
@@ -4074,7 +4171,8 @@
         <v>4</v>
       </c>
       <c r="C99">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>339</v>
@@ -4097,7 +4195,8 @@
         <v>6</v>
       </c>
       <c r="C100">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>333</v>
@@ -4120,7 +4219,8 @@
         <v>5</v>
       </c>
       <c r="C101">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>332</v>
@@ -4143,7 +4243,8 @@
         <v>5</v>
       </c>
       <c r="C102">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>335</v>
@@ -4166,7 +4267,8 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>343</v>
@@ -4189,7 +4291,8 @@
         <v>6</v>
       </c>
       <c r="C104">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>349</v>
@@ -4212,7 +4315,8 @@
         <v>6</v>
       </c>
       <c r="C105">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D105" s="3">
         <v>11</v>
@@ -4235,7 +4339,8 @@
         <v>4</v>
       </c>
       <c r="C106">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>339</v>
@@ -4258,7 +4363,8 @@
         <v>4</v>
       </c>
       <c r="C107">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>339</v>
@@ -4281,7 +4387,8 @@
         <v>6</v>
       </c>
       <c r="C108">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>363</v>
@@ -4304,7 +4411,8 @@
         <v>6</v>
       </c>
       <c r="C109">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>363</v>
@@ -4327,7 +4435,8 @@
         <v>4</v>
       </c>
       <c r="C110">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>344</v>
@@ -4350,7 +4459,8 @@
         <v>4</v>
       </c>
       <c r="C111">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>364</v>
@@ -4373,7 +4483,8 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>344</v>
@@ -4396,7 +4507,8 @@
         <v>4</v>
       </c>
       <c r="C113">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>365</v>
@@ -4419,7 +4531,8 @@
         <v>4</v>
       </c>
       <c r="C114">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>366</v>
@@ -4442,7 +4555,8 @@
         <v>5</v>
       </c>
       <c r="C115">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>340</v>
@@ -4465,7 +4579,8 @@
         <v>5</v>
       </c>
       <c r="C116">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>340</v>
@@ -4488,7 +4603,8 @@
         <v>4</v>
       </c>
       <c r="C117">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>366</v>
@@ -4511,7 +4627,8 @@
         <v>4</v>
       </c>
       <c r="C118">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>367</v>
@@ -4534,7 +4651,8 @@
         <v>4</v>
       </c>
       <c r="C119">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>368</v>
@@ -4557,7 +4675,8 @@
         <v>4</v>
       </c>
       <c r="C120">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>369</v>
@@ -4580,7 +4699,8 @@
         <v>4</v>
       </c>
       <c r="C121">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>343</v>
@@ -4603,7 +4723,8 @@
         <v>4</v>
       </c>
       <c r="C122">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>327</v>
@@ -4626,7 +4747,8 @@
         <v>4</v>
       </c>
       <c r="C123">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>370</v>
@@ -4649,7 +4771,8 @@
         <v>4</v>
       </c>
       <c r="C124">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>327</v>
@@ -4672,7 +4795,8 @@
         <v>6</v>
       </c>
       <c r="C125">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>340</v>
@@ -4695,7 +4819,8 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>371</v>
@@ -4718,7 +4843,8 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>343</v>
@@ -4741,7 +4867,8 @@
         <v>6</v>
       </c>
       <c r="C128">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>340</v>
@@ -4764,7 +4891,8 @@
         <v>4</v>
       </c>
       <c r="C129">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>355</v>
@@ -4787,7 +4915,8 @@
         <v>6</v>
       </c>
       <c r="C130">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="D130" s="3">
         <v>11</v>
@@ -4810,7 +4939,8 @@
         <v>4</v>
       </c>
       <c r="C131">
-        <v>5</v>
+        <f t="shared" ref="C131:C194" si="2">1/1000</f>
+        <v>1E-3</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>372</v>
@@ -4833,7 +4963,8 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>328</v>
@@ -4856,7 +4987,8 @@
         <v>5</v>
       </c>
       <c r="C133">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>323</v>
@@ -4879,7 +5011,8 @@
         <v>4</v>
       </c>
       <c r="C134">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>343</v>
@@ -4902,7 +5035,8 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>335</v>
@@ -4925,7 +5059,8 @@
         <v>6</v>
       </c>
       <c r="C136">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>343</v>
@@ -4948,7 +5083,8 @@
         <v>4</v>
       </c>
       <c r="C137">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>373</v>
@@ -4971,7 +5107,8 @@
         <v>4</v>
       </c>
       <c r="C138">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>374</v>
@@ -4994,7 +5131,8 @@
         <v>4</v>
       </c>
       <c r="C139">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>335</v>
@@ -5017,7 +5155,8 @@
         <v>6</v>
       </c>
       <c r="C140">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>339</v>
@@ -5040,7 +5179,8 @@
         <v>4</v>
       </c>
       <c r="C141">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>375</v>
@@ -5063,7 +5203,8 @@
         <v>4</v>
       </c>
       <c r="C142">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>376</v>
@@ -5086,7 +5227,8 @@
         <v>5</v>
       </c>
       <c r="C143">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>339</v>
@@ -5109,7 +5251,8 @@
         <v>4</v>
       </c>
       <c r="C144">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>377</v>
@@ -5132,7 +5275,8 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>364</v>
@@ -5155,7 +5299,8 @@
         <v>4</v>
       </c>
       <c r="C146">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>343</v>
@@ -5178,7 +5323,8 @@
         <v>4</v>
       </c>
       <c r="C147">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>340</v>
@@ -5201,7 +5347,8 @@
         <v>4</v>
       </c>
       <c r="C148">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>340</v>
@@ -5224,7 +5371,8 @@
         <v>5</v>
       </c>
       <c r="C149">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>378</v>
@@ -5247,7 +5395,8 @@
         <v>4</v>
       </c>
       <c r="C150">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>379</v>
@@ -5270,7 +5419,8 @@
         <v>4</v>
       </c>
       <c r="C151">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>340</v>
@@ -5293,7 +5443,8 @@
         <v>5</v>
       </c>
       <c r="C152">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>380</v>
@@ -5316,7 +5467,8 @@
         <v>5</v>
       </c>
       <c r="C153">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>365</v>
@@ -5339,7 +5491,8 @@
         <v>5</v>
       </c>
       <c r="C154">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>381</v>
@@ -5362,7 +5515,8 @@
         <v>6</v>
       </c>
       <c r="C155">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>382</v>
@@ -5385,7 +5539,8 @@
         <v>4</v>
       </c>
       <c r="C156">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>383</v>
@@ -5408,7 +5563,8 @@
         <v>5</v>
       </c>
       <c r="C157">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>327</v>
@@ -5431,7 +5587,8 @@
         <v>5</v>
       </c>
       <c r="C158">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>384</v>
@@ -5454,7 +5611,8 @@
         <v>5</v>
       </c>
       <c r="C159">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>323</v>
@@ -5477,7 +5635,8 @@
         <v>5</v>
       </c>
       <c r="C160">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>340</v>
@@ -5500,7 +5659,8 @@
         <v>5</v>
       </c>
       <c r="C161">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>340</v>
@@ -5523,7 +5683,8 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>340</v>
@@ -5546,7 +5707,8 @@
         <v>4</v>
       </c>
       <c r="C163">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>322</v>
@@ -5569,7 +5731,8 @@
         <v>4</v>
       </c>
       <c r="C164">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>339</v>
@@ -5592,7 +5755,8 @@
         <v>4</v>
       </c>
       <c r="C165">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>339</v>
@@ -5615,7 +5779,8 @@
         <v>4</v>
       </c>
       <c r="C166">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>385</v>
@@ -5638,7 +5803,8 @@
         <v>4</v>
       </c>
       <c r="C167">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>385</v>
@@ -5661,7 +5827,8 @@
         <v>4</v>
       </c>
       <c r="C168">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>328</v>
@@ -5684,7 +5851,8 @@
         <v>4</v>
       </c>
       <c r="C169">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>328</v>
@@ -5707,7 +5875,8 @@
         <v>4</v>
       </c>
       <c r="C170">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>386</v>
@@ -5730,7 +5899,8 @@
         <v>4</v>
       </c>
       <c r="C171">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>343</v>
@@ -5753,7 +5923,8 @@
         <v>4</v>
       </c>
       <c r="C172">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>322</v>
@@ -5776,7 +5947,8 @@
         <v>6</v>
       </c>
       <c r="C173">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>339</v>
@@ -5799,7 +5971,8 @@
         <v>4</v>
       </c>
       <c r="C174">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>344</v>
@@ -5822,7 +5995,8 @@
         <v>4</v>
       </c>
       <c r="C175">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>340</v>
@@ -5845,7 +6019,8 @@
         <v>4</v>
       </c>
       <c r="C176">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>358</v>
@@ -5868,7 +6043,8 @@
         <v>4</v>
       </c>
       <c r="C177">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>340</v>
@@ -5891,7 +6067,8 @@
         <v>4</v>
       </c>
       <c r="C178">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D178" s="3" t="s">
         <v>340</v>
@@ -5914,7 +6091,8 @@
         <v>4</v>
       </c>
       <c r="C179">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>387</v>
@@ -5937,7 +6115,8 @@
         <v>4</v>
       </c>
       <c r="C180">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D180" s="3" t="s">
         <v>362</v>
@@ -5960,7 +6139,8 @@
         <v>4</v>
       </c>
       <c r="C181">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>372</v>
@@ -5983,7 +6163,8 @@
         <v>6</v>
       </c>
       <c r="C182">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>343</v>
@@ -6006,7 +6187,8 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>364</v>
@@ -6029,7 +6211,8 @@
         <v>5</v>
       </c>
       <c r="C184">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>327</v>
@@ -6052,7 +6235,8 @@
         <v>5</v>
       </c>
       <c r="C185">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D185" s="3" t="s">
         <v>327</v>
@@ -6075,7 +6259,8 @@
         <v>4</v>
       </c>
       <c r="C186">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D186" s="3" t="s">
         <v>332</v>
@@ -6098,7 +6283,8 @@
         <v>6</v>
       </c>
       <c r="C187">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D187" s="3" t="s">
         <v>343</v>
@@ -6121,7 +6307,8 @@
         <v>4</v>
       </c>
       <c r="C188">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D188" s="3" t="s">
         <v>388</v>
@@ -6144,7 +6331,8 @@
         <v>4</v>
       </c>
       <c r="C189">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D189" s="3" t="s">
         <v>327</v>
@@ -6167,7 +6355,8 @@
         <v>4</v>
       </c>
       <c r="C190">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D190" s="3" t="s">
         <v>327</v>
@@ -6190,7 +6379,8 @@
         <v>6</v>
       </c>
       <c r="C191">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D191" s="3" t="s">
         <v>364</v>
@@ -6213,7 +6403,8 @@
         <v>6</v>
       </c>
       <c r="C192">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>340</v>
@@ -6236,7 +6427,8 @@
         <v>4</v>
       </c>
       <c r="C193">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>332</v>
@@ -6259,7 +6451,8 @@
         <v>6</v>
       </c>
       <c r="C194">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>1E-3</v>
       </c>
       <c r="D194" s="3">
         <v>11</v>
@@ -6282,7 +6475,8 @@
         <v>6</v>
       </c>
       <c r="C195">
-        <v>5</v>
+        <f t="shared" ref="C195:C258" si="3">1/1000</f>
+        <v>1E-3</v>
       </c>
       <c r="D195" s="3">
         <v>11</v>
@@ -6305,7 +6499,8 @@
         <v>4</v>
       </c>
       <c r="C196">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D196" s="3" t="s">
         <v>389</v>
@@ -6328,7 +6523,8 @@
         <v>4</v>
       </c>
       <c r="C197">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>390</v>
@@ -6351,7 +6547,8 @@
         <v>4</v>
       </c>
       <c r="C198">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>322</v>
@@ -6374,7 +6571,8 @@
         <v>430</v>
       </c>
       <c r="C199">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>391</v>
@@ -6397,7 +6595,8 @@
         <v>6</v>
       </c>
       <c r="C200">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>364</v>
@@ -6420,7 +6619,8 @@
         <v>6</v>
       </c>
       <c r="C201">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D201" s="3" t="s">
         <v>392</v>
@@ -6443,7 +6643,8 @@
         <v>4</v>
       </c>
       <c r="C202">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>393</v>
@@ -6466,7 +6667,8 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D203" s="3" t="s">
         <v>394</v>
@@ -6489,7 +6691,8 @@
         <v>4</v>
       </c>
       <c r="C204">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D204" s="3" t="s">
         <v>340</v>
@@ -6512,7 +6715,8 @@
         <v>4</v>
       </c>
       <c r="C205">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D205" s="3" t="s">
         <v>370</v>
@@ -6535,7 +6739,8 @@
         <v>5</v>
       </c>
       <c r="C206">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>395</v>
@@ -6558,7 +6763,8 @@
         <v>5</v>
       </c>
       <c r="C207">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>396</v>
@@ -6581,7 +6787,8 @@
         <v>6</v>
       </c>
       <c r="C208">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D208" s="3">
         <v>11</v>
@@ -6604,7 +6811,8 @@
         <v>5</v>
       </c>
       <c r="C209">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>327</v>
@@ -6627,7 +6835,8 @@
         <v>4</v>
       </c>
       <c r="C210">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D210" s="3" t="s">
         <v>397</v>
@@ -6650,7 +6859,8 @@
         <v>4</v>
       </c>
       <c r="C211">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D211" s="3" t="s">
         <v>368</v>
@@ -6673,7 +6883,8 @@
         <v>6</v>
       </c>
       <c r="C212">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D212" s="3" t="s">
         <v>364</v>
@@ -6696,7 +6907,8 @@
         <v>4</v>
       </c>
       <c r="C213">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D213" s="3" t="s">
         <v>327</v>
@@ -6719,7 +6931,8 @@
         <v>4</v>
       </c>
       <c r="C214">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>337</v>
@@ -6742,7 +6955,8 @@
         <v>4</v>
       </c>
       <c r="C215">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>398</v>
@@ -6765,7 +6979,8 @@
         <v>4</v>
       </c>
       <c r="C216">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>344</v>
@@ -6788,7 +7003,8 @@
         <v>4</v>
       </c>
       <c r="C217">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>333</v>
@@ -6811,7 +7027,8 @@
         <v>4</v>
       </c>
       <c r="C218">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>399</v>
@@ -6834,7 +7051,8 @@
         <v>4</v>
       </c>
       <c r="C219">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D219" s="3" t="s">
         <v>361</v>
@@ -6857,7 +7075,8 @@
         <v>6</v>
       </c>
       <c r="C220">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D220" s="3" t="s">
         <v>339</v>
@@ -6880,7 +7099,8 @@
         <v>4</v>
       </c>
       <c r="C221">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D221" s="3" t="s">
         <v>339</v>
@@ -6903,7 +7123,8 @@
         <v>4</v>
       </c>
       <c r="C222">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D222" s="3" t="s">
         <v>328</v>
@@ -6926,7 +7147,8 @@
         <v>4</v>
       </c>
       <c r="C223">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D223" s="3" t="s">
         <v>370</v>
@@ -6949,7 +7171,8 @@
         <v>4</v>
       </c>
       <c r="C224">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>400</v>
@@ -6972,7 +7195,8 @@
         <v>4</v>
       </c>
       <c r="C225">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>401</v>
@@ -6995,7 +7219,8 @@
         <v>4</v>
       </c>
       <c r="C226">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D226" s="3" t="s">
         <v>327</v>
@@ -7018,7 +7243,8 @@
         <v>4</v>
       </c>
       <c r="C227">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>402</v>
@@ -7041,7 +7267,8 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>340</v>
@@ -7064,7 +7291,8 @@
         <v>4</v>
       </c>
       <c r="C229">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>337</v>
@@ -7087,7 +7315,8 @@
         <v>4</v>
       </c>
       <c r="C230">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D230" s="3" t="s">
         <v>403</v>
@@ -7110,7 +7339,8 @@
         <v>4</v>
       </c>
       <c r="C231">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>404</v>
@@ -7133,7 +7363,8 @@
         <v>4</v>
       </c>
       <c r="C232">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D232" s="3" t="s">
         <v>364</v>
@@ -7156,7 +7387,8 @@
         <v>4</v>
       </c>
       <c r="C233">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>364</v>
@@ -7179,7 +7411,8 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>405</v>
@@ -7202,7 +7435,8 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D235" s="3" t="s">
         <v>405</v>
@@ -7225,7 +7459,8 @@
         <v>4</v>
       </c>
       <c r="C236">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D236" s="3" t="s">
         <v>337</v>
@@ -7248,7 +7483,8 @@
         <v>4</v>
       </c>
       <c r="C237">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D237" s="3" t="s">
         <v>327</v>
@@ -7271,7 +7507,8 @@
         <v>4</v>
       </c>
       <c r="C238">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D238" s="3" t="s">
         <v>340</v>
@@ -7294,7 +7531,8 @@
         <v>4</v>
       </c>
       <c r="C239">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D239" s="3" t="s">
         <v>385</v>
@@ -7317,7 +7555,8 @@
         <v>4</v>
       </c>
       <c r="C240">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D240" s="3" t="s">
         <v>385</v>
@@ -7340,7 +7579,8 @@
         <v>4</v>
       </c>
       <c r="C241">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D241" s="3" t="s">
         <v>385</v>
@@ -7363,7 +7603,8 @@
         <v>4</v>
       </c>
       <c r="C242">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D242" s="3" t="s">
         <v>406</v>
@@ -7386,7 +7627,8 @@
         <v>4</v>
       </c>
       <c r="C243">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D243" s="3" t="s">
         <v>327</v>
@@ -7409,7 +7651,8 @@
         <v>6</v>
       </c>
       <c r="C244">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D244" s="3">
         <v>11</v>
@@ -7432,7 +7675,8 @@
         <v>5</v>
       </c>
       <c r="C245">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>344</v>
@@ -7455,7 +7699,8 @@
         <v>5</v>
       </c>
       <c r="C246">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D246" s="3" t="s">
         <v>340</v>
@@ -7478,7 +7723,8 @@
         <v>4</v>
       </c>
       <c r="C247">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D247" s="3" t="s">
         <v>322</v>
@@ -7501,7 +7747,8 @@
         <v>4</v>
       </c>
       <c r="C248">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>407</v>
@@ -7524,7 +7771,8 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D249" s="3" t="s">
         <v>364</v>
@@ -7547,7 +7795,8 @@
         <v>5</v>
       </c>
       <c r="C250">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D250" s="3" t="s">
         <v>343</v>
@@ -7570,7 +7819,8 @@
         <v>4</v>
       </c>
       <c r="C251">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D251" s="3" t="s">
         <v>327</v>
@@ -7593,7 +7843,8 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D252" s="3" t="s">
         <v>364</v>
@@ -7616,7 +7867,8 @@
         <v>4</v>
       </c>
       <c r="C253">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D253" s="3" t="s">
         <v>408</v>
@@ -7639,7 +7891,8 @@
         <v>4</v>
       </c>
       <c r="C254">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D254" s="3" t="s">
         <v>322</v>
@@ -7662,7 +7915,8 @@
         <v>6</v>
       </c>
       <c r="C255">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D255" s="3" t="s">
         <v>339</v>
@@ -7685,7 +7939,8 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D256" s="3" t="s">
         <v>339</v>
@@ -7708,7 +7963,8 @@
         <v>4</v>
       </c>
       <c r="C257">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D257" s="3" t="s">
         <v>340</v>
@@ -7731,7 +7987,8 @@
         <v>5</v>
       </c>
       <c r="C258">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
       </c>
       <c r="D258" s="3" t="s">
         <v>409</v>
@@ -7754,7 +8011,8 @@
         <v>4</v>
       </c>
       <c r="C259">
-        <v>5</v>
+        <f t="shared" ref="C259:C312" si="4">1/1000</f>
+        <v>1E-3</v>
       </c>
       <c r="D259" s="3" t="s">
         <v>410</v>
@@ -7777,7 +8035,8 @@
         <v>4</v>
       </c>
       <c r="C260">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D260" s="3" t="s">
         <v>411</v>
@@ -7800,7 +8059,8 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D261" s="3" t="s">
         <v>412</v>
@@ -7823,7 +8083,8 @@
         <v>4</v>
       </c>
       <c r="C262">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D262" s="3" t="s">
         <v>340</v>
@@ -7846,7 +8107,8 @@
         <v>4</v>
       </c>
       <c r="C263">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D263" s="3" t="s">
         <v>327</v>
@@ -7869,7 +8131,8 @@
         <v>5</v>
       </c>
       <c r="C264">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D264" s="3" t="s">
         <v>327</v>
@@ -7892,7 +8155,8 @@
         <v>4</v>
       </c>
       <c r="C265">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D265" s="3" t="s">
         <v>333</v>
@@ -7915,7 +8179,8 @@
         <v>4</v>
       </c>
       <c r="C266">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D266" s="3" t="s">
         <v>343</v>
@@ -7938,7 +8203,8 @@
         <v>6</v>
       </c>
       <c r="C267">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D267" s="3">
         <v>11</v>
@@ -7961,7 +8227,8 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D268" s="3">
         <v>11</v>
@@ -7984,7 +8251,8 @@
         <v>6</v>
       </c>
       <c r="C269">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D269" s="3" t="s">
         <v>413</v>
@@ -8007,7 +8275,8 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D270" s="3" t="s">
         <v>339</v>
@@ -8030,7 +8299,8 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D271" s="3" t="s">
         <v>339</v>
@@ -8053,7 +8323,8 @@
         <v>429</v>
       </c>
       <c r="C272">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>414</v>
@@ -8076,7 +8347,8 @@
         <v>429</v>
       </c>
       <c r="C273">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D273" s="3" t="s">
         <v>415</v>
@@ -8099,7 +8371,8 @@
         <v>429</v>
       </c>
       <c r="C274">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D274" s="3" t="s">
         <v>416</v>
@@ -8122,7 +8395,8 @@
         <v>429</v>
       </c>
       <c r="C275">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D275" s="3" t="s">
         <v>417</v>
@@ -8145,7 +8419,8 @@
         <v>429</v>
       </c>
       <c r="C276">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D276" s="3" t="s">
         <v>417</v>
@@ -8168,7 +8443,8 @@
         <v>5</v>
       </c>
       <c r="C277">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D277" s="3" t="s">
         <v>364</v>
@@ -8191,7 +8467,8 @@
         <v>5</v>
       </c>
       <c r="C278">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D278" s="3" t="s">
         <v>418</v>
@@ -8214,7 +8491,8 @@
         <v>4</v>
       </c>
       <c r="C279">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D279" s="3" t="s">
         <v>351</v>
@@ -8237,7 +8515,8 @@
         <v>4</v>
       </c>
       <c r="C280">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>337</v>
@@ -8260,7 +8539,8 @@
         <v>4</v>
       </c>
       <c r="C281">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D281" s="3" t="s">
         <v>365</v>
@@ -8283,7 +8563,8 @@
         <v>4</v>
       </c>
       <c r="C282">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D282" s="3" t="s">
         <v>419</v>
@@ -8306,7 +8587,8 @@
         <v>5</v>
       </c>
       <c r="C283">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D283" s="3" t="s">
         <v>340</v>
@@ -8329,7 +8611,8 @@
         <v>5</v>
       </c>
       <c r="C284">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D284" s="3" t="s">
         <v>340</v>
@@ -8352,7 +8635,8 @@
         <v>5</v>
       </c>
       <c r="C285">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D285" s="3" t="s">
         <v>340</v>
@@ -8375,7 +8659,8 @@
         <v>4</v>
       </c>
       <c r="C286">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D286" s="3" t="s">
         <v>359</v>
@@ -8398,7 +8683,8 @@
         <v>6</v>
       </c>
       <c r="C287">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D287" s="3">
         <v>11</v>
@@ -8421,7 +8707,8 @@
         <v>4</v>
       </c>
       <c r="C288">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>327</v>
@@ -8444,7 +8731,8 @@
         <v>5</v>
       </c>
       <c r="C289">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D289" s="3" t="s">
         <v>340</v>
@@ -8467,7 +8755,8 @@
         <v>4</v>
       </c>
       <c r="C290">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D290" s="3" t="s">
         <v>344</v>
@@ -8490,7 +8779,8 @@
         <v>4</v>
       </c>
       <c r="C291">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D291" s="3" t="s">
         <v>420</v>
@@ -8513,7 +8803,8 @@
         <v>4</v>
       </c>
       <c r="C292">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D292" s="3" t="s">
         <v>421</v>
@@ -8536,7 +8827,8 @@
         <v>4</v>
       </c>
       <c r="C293">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D293" s="3" t="s">
         <v>358</v>
@@ -8559,7 +8851,8 @@
         <v>6</v>
       </c>
       <c r="C294">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D294" s="3" t="s">
         <v>343</v>
@@ -8582,7 +8875,8 @@
         <v>6</v>
       </c>
       <c r="C295">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D295" s="3" t="s">
         <v>332</v>
@@ -8605,7 +8899,8 @@
         <v>5</v>
       </c>
       <c r="C296">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D296" s="3" t="s">
         <v>422</v>
@@ -8628,7 +8923,8 @@
         <v>4</v>
       </c>
       <c r="C297">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D297" s="3" t="s">
         <v>372</v>
@@ -8651,7 +8947,8 @@
         <v>4</v>
       </c>
       <c r="C298">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D298" s="3" t="s">
         <v>337</v>
@@ -8674,7 +8971,8 @@
         <v>4</v>
       </c>
       <c r="C299">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D299" s="3" t="s">
         <v>339</v>
@@ -8697,7 +8995,8 @@
         <v>4</v>
       </c>
       <c r="C300">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D300" s="3" t="s">
         <v>365</v>
@@ -8720,7 +9019,8 @@
         <v>4</v>
       </c>
       <c r="C301">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D301" s="3" t="s">
         <v>423</v>
@@ -8743,7 +9043,8 @@
         <v>4</v>
       </c>
       <c r="C302">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D302" s="3" t="s">
         <v>424</v>
@@ -8766,7 +9067,8 @@
         <v>4</v>
       </c>
       <c r="C303">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D303" s="3" t="s">
         <v>327</v>
@@ -8789,7 +9091,8 @@
         <v>4</v>
       </c>
       <c r="C304">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D304" s="3" t="s">
         <v>343</v>
@@ -8812,7 +9115,8 @@
         <v>5</v>
       </c>
       <c r="C305">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D305" s="3" t="s">
         <v>319</v>
@@ -8835,7 +9139,8 @@
         <v>4</v>
       </c>
       <c r="C306">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D306" s="3" t="s">
         <v>425</v>
@@ -8858,7 +9163,8 @@
         <v>4</v>
       </c>
       <c r="C307">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D307" s="3" t="s">
         <v>370</v>
@@ -8881,7 +9187,8 @@
         <v>4</v>
       </c>
       <c r="C308">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D308" s="3" t="s">
         <v>426</v>
@@ -8904,7 +9211,8 @@
         <v>6</v>
       </c>
       <c r="C309">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D309" s="3" t="s">
         <v>427</v>
@@ -8927,7 +9235,8 @@
         <v>4</v>
       </c>
       <c r="C310">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D310" s="3" t="s">
         <v>373</v>
@@ -8950,7 +9259,8 @@
         <v>4</v>
       </c>
       <c r="C311">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D311" s="3" t="s">
         <v>428</v>
@@ -8973,7 +9283,8 @@
         <v>4</v>
       </c>
       <c r="C312">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
       </c>
       <c r="D312" s="3" t="s">
         <v>319</v>

--- a/Thesis/developer_states.xlsx
+++ b/Thesis/developer_states.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/abigail_weeks_rmi_org/Documents/Documents/GitHub/Thesis/Thesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="258" documentId="8_{A4B64DE1-C1F9-4DF8-A805-E80C52345F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DB9B39E-0EE8-4C09-A485-2566A200D2DF}"/>
+  <xr:revisionPtr revIDLastSave="264" documentId="8_{A4B64DE1-C1F9-4DF8-A805-E80C52345F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F45BABC-6B5F-470E-96B2-DA3D3AFCA013}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31558D2F-F994-4500-BC80-1C41F5323AB0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{31558D2F-F994-4500-BC80-1C41F5323AB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="339">
   <si>
     <t>unique_id</t>
   </si>
@@ -996,336 +996,6 @@
   </si>
   <si>
     <t>AF1-116</t>
-  </si>
-  <si>
-    <t>120.0</t>
-  </si>
-  <si>
-    <t>109.3</t>
-  </si>
-  <si>
-    <t>440.0</t>
-  </si>
-  <si>
-    <t>60.0</t>
-  </si>
-  <si>
-    <t>40.0</t>
-  </si>
-  <si>
-    <t>8.4</t>
-  </si>
-  <si>
-    <t>18.15</t>
-  </si>
-  <si>
-    <t>294.7</t>
-  </si>
-  <si>
-    <t>150.0</t>
-  </si>
-  <si>
-    <t>30.0</t>
-  </si>
-  <si>
-    <t>299.0</t>
-  </si>
-  <si>
-    <t>62.4</t>
-  </si>
-  <si>
-    <t>43.2</t>
-  </si>
-  <si>
-    <t>200.0</t>
-  </si>
-  <si>
-    <t>500.0</t>
-  </si>
-  <si>
-    <t>95.1</t>
-  </si>
-  <si>
-    <t>300.0</t>
-  </si>
-  <si>
-    <t>118.6</t>
-  </si>
-  <si>
-    <t>90.0</t>
-  </si>
-  <si>
-    <t>144.0</t>
-  </si>
-  <si>
-    <t>100.0</t>
-  </si>
-  <si>
-    <t>20.0</t>
-  </si>
-  <si>
-    <t>42.2</t>
-  </si>
-  <si>
-    <t>79.5</t>
-  </si>
-  <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>80.0</t>
-  </si>
-  <si>
-    <t>199.0</t>
-  </si>
-  <si>
-    <t>175.0</t>
-  </si>
-  <si>
-    <t>255.0</t>
-  </si>
-  <si>
-    <t>180.0</t>
-  </si>
-  <si>
-    <t>52.2</t>
-  </si>
-  <si>
-    <t>299.97</t>
-  </si>
-  <si>
-    <t>260.0</t>
-  </si>
-  <si>
-    <t>212.0</t>
-  </si>
-  <si>
-    <t>190.89</t>
-  </si>
-  <si>
-    <t>346.0</t>
-  </si>
-  <si>
-    <t>140.0</t>
-  </si>
-  <si>
-    <t>210.0</t>
-  </si>
-  <si>
-    <t>450.0</t>
-  </si>
-  <si>
-    <t>55.0</t>
-  </si>
-  <si>
-    <t>125.0</t>
-  </si>
-  <si>
-    <t>800.0</t>
-  </si>
-  <si>
-    <t>54.0</t>
-  </si>
-  <si>
-    <t>25.0</t>
-  </si>
-  <si>
-    <t>35.0</t>
-  </si>
-  <si>
-    <t>75.0</t>
-  </si>
-  <si>
-    <t>250.0</t>
-  </si>
-  <si>
-    <t>126.0</t>
-  </si>
-  <si>
-    <t>19.99</t>
-  </si>
-  <si>
-    <t>18.0</t>
-  </si>
-  <si>
-    <t>23.0</t>
-  </si>
-  <si>
-    <t>70.0</t>
-  </si>
-  <si>
-    <t>240.0</t>
-  </si>
-  <si>
-    <t>65.0</t>
-  </si>
-  <si>
-    <t>98.0</t>
-  </si>
-  <si>
-    <t>206.6</t>
-  </si>
-  <si>
-    <t>148.0</t>
-  </si>
-  <si>
-    <t>12.0</t>
-  </si>
-  <si>
-    <t>15.75</t>
-  </si>
-  <si>
-    <t>95.0</t>
-  </si>
-  <si>
-    <t>19.9</t>
-  </si>
-  <si>
-    <t>126.5</t>
-  </si>
-  <si>
-    <t>202.4</t>
-  </si>
-  <si>
-    <t>197.2</t>
-  </si>
-  <si>
-    <t>77.0</t>
-  </si>
-  <si>
-    <t>53.9</t>
-  </si>
-  <si>
-    <t>15.0</t>
-  </si>
-  <si>
-    <t>174.8</t>
-  </si>
-  <si>
-    <t>41.0</t>
-  </si>
-  <si>
-    <t>46.8</t>
-  </si>
-  <si>
-    <t>127.0</t>
-  </si>
-  <si>
-    <t>53.0</t>
-  </si>
-  <si>
-    <t>569.0</t>
-  </si>
-  <si>
-    <t>122.0</t>
-  </si>
-  <si>
-    <t>314.0</t>
-  </si>
-  <si>
-    <t>74.5</t>
-  </si>
-  <si>
-    <t>127.86</t>
-  </si>
-  <si>
-    <t>130.0</t>
-  </si>
-  <si>
-    <t>82.5</t>
-  </si>
-  <si>
-    <t>36.0</t>
-  </si>
-  <si>
-    <t>72.0</t>
-  </si>
-  <si>
-    <t>63.0</t>
-  </si>
-  <si>
-    <t>94.0</t>
-  </si>
-  <si>
-    <t>117.0</t>
-  </si>
-  <si>
-    <t>107.0</t>
-  </si>
-  <si>
-    <t>118.56</t>
-  </si>
-  <si>
-    <t>26.0</t>
-  </si>
-  <si>
-    <t>10.0</t>
-  </si>
-  <si>
-    <t>102.0</t>
-  </si>
-  <si>
-    <t>62.0</t>
-  </si>
-  <si>
-    <t>62.5</t>
-  </si>
-  <si>
-    <t>14.2</t>
-  </si>
-  <si>
-    <t>128.0</t>
-  </si>
-  <si>
-    <t>160.0</t>
-  </si>
-  <si>
-    <t>127.5</t>
-  </si>
-  <si>
-    <t>833.0</t>
-  </si>
-  <si>
-    <t>836.0</t>
-  </si>
-  <si>
-    <t>820.0</t>
-  </si>
-  <si>
-    <t>800.1</t>
-  </si>
-  <si>
-    <t>79.0</t>
-  </si>
-  <si>
-    <t>167.0</t>
-  </si>
-  <si>
-    <t>188.5</t>
-  </si>
-  <si>
-    <t>45.0</t>
-  </si>
-  <si>
-    <t>106.0</t>
-  </si>
-  <si>
-    <t>225.0</t>
-  </si>
-  <si>
-    <t>222.0</t>
-  </si>
-  <si>
-    <t>82.0</t>
-  </si>
-  <si>
-    <t>57.0</t>
-  </si>
-  <si>
-    <t>22.0</t>
-  </si>
-  <si>
-    <t>64.2</t>
   </si>
   <si>
     <t>wind_offshore</t>
@@ -1449,7 +1119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1464,6 +1134,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1802,7 +1475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB29B94B-9539-40D3-B7DF-08904E974596}">
-  <dimension ref="A1:G312"/>
+  <dimension ref="A1:I312"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.7265625" customWidth="1"/>
@@ -1812,7 +1485,7 @@
     <col min="5" max="5" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1826,16 +1499,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>448</v>
+        <v>338</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>431</v>
+        <v>321</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1846,20 +1519,20 @@
         <f>1/1000</f>
         <v>1E-3</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>319</v>
+      <c r="D2" s="6">
+        <v>120</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>432</v>
+        <v>322</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1870,68 +1543,68 @@
         <f t="shared" ref="C3:C66" si="0">1/1000</f>
         <v>1E-3</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>320</v>
+      <c r="D3" s="6">
+        <v>109.3</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>432</v>
+        <v>322</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>429</v>
+        <v>319</v>
       </c>
       <c r="C4">
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>321</v>
+      <c r="D4" s="6">
+        <v>440</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>432</v>
+        <v>322</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>429</v>
+        <v>319</v>
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>321</v>
+      <c r="D5" s="6">
+        <v>440</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>432</v>
+        <v>322</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1942,20 +1615,20 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>322</v>
+      <c r="D6" s="6">
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1966,20 +1639,20 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>323</v>
+      <c r="D7" s="6">
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1990,20 +1663,24 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>324</v>
+      <c r="D8" s="6">
+        <v>8.4</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+      <c r="I8" s="5">
+        <f>SUM(D:D)</f>
+        <v>40783.17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -2014,20 +1691,20 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>325</v>
+      <c r="D9" s="6">
+        <v>18.149999999999999</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -2038,20 +1715,20 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>326</v>
+      <c r="D10" s="6">
+        <v>294.7</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -2062,20 +1739,20 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>327</v>
+      <c r="D11" s="6">
+        <v>150</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -2086,20 +1763,20 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>328</v>
+      <c r="D12" s="6">
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -2110,20 +1787,20 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>329</v>
+      <c r="D13" s="6">
+        <v>299</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2134,20 +1811,20 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>330</v>
+      <c r="D14" s="6">
+        <v>62.4</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -2158,20 +1835,20 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>331</v>
+      <c r="D15" s="6">
+        <v>43.2</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -2182,17 +1859,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>332</v>
+      <c r="D16" s="6">
+        <v>200</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -2206,17 +1883,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>333</v>
+      <c r="D17" s="6">
+        <v>500</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -2230,17 +1907,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>334</v>
+      <c r="D18" s="6">
+        <v>95.1</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -2254,17 +1931,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>335</v>
+      <c r="D19" s="6">
+        <v>300</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -2278,17 +1955,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>335</v>
+      <c r="D20" s="6">
+        <v>300</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -2302,17 +1979,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>336</v>
+      <c r="D21" s="6">
+        <v>118.6</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -2326,17 +2003,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>332</v>
+      <c r="D22" s="6">
+        <v>200</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -2350,17 +2027,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>337</v>
+      <c r="D23" s="6">
+        <v>90</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -2374,17 +2051,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>338</v>
+      <c r="D24" s="6">
+        <v>144</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -2398,17 +2075,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>339</v>
+      <c r="D25" s="6">
+        <v>100</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>31</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -2422,17 +2099,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>340</v>
+      <c r="D26" s="6">
+        <v>20</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -2446,17 +2123,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>341</v>
+      <c r="D27" s="6">
+        <v>42.2</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -2470,17 +2147,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>340</v>
+      <c r="D28" s="6">
+        <v>20</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>34</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -2494,17 +2171,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>327</v>
+      <c r="D29" s="6">
+        <v>150</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -2518,17 +2195,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>339</v>
+      <c r="D30" s="6">
+        <v>100</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -2542,17 +2219,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>342</v>
+      <c r="D31" s="6">
+        <v>79.5</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>37</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -2566,17 +2243,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>327</v>
+      <c r="D32" s="6">
+        <v>150</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>38</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -2590,17 +2267,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>327</v>
+      <c r="D33" s="6">
+        <v>150</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>39</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -2614,17 +2291,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>343</v>
+      <c r="D34" s="6">
+        <v>50</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>40</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -2638,17 +2315,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>343</v>
+      <c r="D35" s="6">
+        <v>50</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -2662,17 +2339,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>335</v>
+      <c r="D36" s="6">
+        <v>300</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>447</v>
+        <v>337</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -2686,17 +2363,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>344</v>
+      <c r="D37" s="6">
+        <v>80</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -2710,17 +2387,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>345</v>
+      <c r="D38" s="6">
+        <v>199</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -2734,17 +2411,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>339</v>
+      <c r="D39" s="6">
+        <v>100</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -2758,17 +2435,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>332</v>
+      <c r="D40" s="6">
+        <v>200</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
@@ -2782,17 +2459,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>335</v>
+      <c r="D41" s="6">
+        <v>300</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>47</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
@@ -2806,17 +2483,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>332</v>
+      <c r="D42" s="6">
+        <v>200</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>447</v>
+        <v>337</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -2830,17 +2507,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>340</v>
+      <c r="D43" s="6">
+        <v>20</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
@@ -2854,17 +2531,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>346</v>
+      <c r="D44" s="6">
+        <v>175</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>50</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
@@ -2885,10 +2562,10 @@
         <v>51</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
@@ -2909,10 +2586,10 @@
         <v>52</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
@@ -2926,17 +2603,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>332</v>
+      <c r="D47" s="6">
+        <v>200</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>53</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
@@ -2950,17 +2627,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>347</v>
+      <c r="D48" s="6">
+        <v>255</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -2974,17 +2651,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>348</v>
+      <c r="D49" s="6">
+        <v>180</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -2998,17 +2675,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>349</v>
+      <c r="D50" s="6">
+        <v>52.2</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -3022,17 +2699,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>339</v>
+      <c r="D51" s="6">
+        <v>100</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3046,17 +2723,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>335</v>
+      <c r="D52" s="6">
+        <v>300</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>447</v>
+        <v>337</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -3070,17 +2747,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>327</v>
+      <c r="D53" s="6">
+        <v>150</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>59</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -3094,17 +2771,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>327</v>
+      <c r="D54" s="6">
+        <v>150</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>60</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3118,17 +2795,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>343</v>
+      <c r="D55" s="6">
+        <v>50</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3142,17 +2819,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>335</v>
+      <c r="D56" s="6">
+        <v>300</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>62</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3166,17 +2843,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>335</v>
+      <c r="D57" s="6">
+        <v>300</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>63</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3190,17 +2867,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>327</v>
+      <c r="D58" s="6">
+        <v>150</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>64</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -3214,17 +2891,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>327</v>
+      <c r="D59" s="6">
+        <v>150</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>65</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -3238,17 +2915,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>339</v>
+      <c r="D60" s="6">
+        <v>100</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -3262,17 +2939,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>327</v>
+      <c r="D61" s="6">
+        <v>150</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>67</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3286,17 +2963,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>350</v>
+      <c r="D62" s="6">
+        <v>299.97000000000003</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>68</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -3310,17 +2987,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>351</v>
+      <c r="D63" s="6">
+        <v>260</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>447</v>
+        <v>337</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -3334,17 +3011,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>352</v>
+      <c r="D64" s="6">
+        <v>212</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
@@ -3358,17 +3035,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>332</v>
+      <c r="D65" s="6">
+        <v>200</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>71</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
@@ -3382,17 +3059,17 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>347</v>
+      <c r="D66" s="6">
+        <v>255</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>72</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
@@ -3406,17 +3083,17 @@
         <f t="shared" ref="C67:C130" si="1">1/1000</f>
         <v>1E-3</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>353</v>
+      <c r="D67" s="6">
+        <v>190.89</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
@@ -3424,7 +3101,7 @@
         <v>74</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>430</v>
+        <v>320</v>
       </c>
       <c r="C68">
         <f t="shared" si="1"/>
@@ -3437,10 +3114,10 @@
         <v>74</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
@@ -3454,17 +3131,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>335</v>
+      <c r="D69" s="6">
+        <v>300</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
@@ -3478,17 +3155,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>332</v>
+      <c r="D70" s="6">
+        <v>200</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>76</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
@@ -3502,17 +3179,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>354</v>
+      <c r="D71" s="6">
+        <v>346</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>77</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
@@ -3526,17 +3203,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>339</v>
+      <c r="D72" s="6">
+        <v>100</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>78</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
@@ -3550,17 +3227,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>339</v>
+      <c r="D73" s="6">
+        <v>100</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
@@ -3574,17 +3251,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>339</v>
+      <c r="D74" s="6">
+        <v>100</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
@@ -3598,17 +3275,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>327</v>
+      <c r="D75" s="6">
+        <v>150</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>81</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
@@ -3622,17 +3299,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>332</v>
+      <c r="D76" s="6">
+        <v>200</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>82</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
@@ -3646,17 +3323,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>332</v>
+      <c r="D77" s="6">
+        <v>200</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
@@ -3677,10 +3354,10 @@
         <v>84</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
@@ -3694,17 +3371,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>339</v>
+      <c r="D79" s="6">
+        <v>100</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
@@ -3718,17 +3395,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>355</v>
+      <c r="D80" s="6">
+        <v>140</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
@@ -3742,17 +3419,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>339</v>
+      <c r="D81" s="6">
+        <v>100</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>87</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
@@ -3766,17 +3443,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>356</v>
+      <c r="D82" s="6">
+        <v>210</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>88</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
@@ -3790,17 +3467,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>357</v>
+      <c r="D83" s="6">
+        <v>450</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
@@ -3814,17 +3491,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>348</v>
+      <c r="D84" s="6">
+        <v>180</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>90</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
@@ -3838,17 +3515,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>358</v>
+      <c r="D85" s="6">
+        <v>55</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>91</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
@@ -3862,17 +3539,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D86" s="3" t="s">
-        <v>359</v>
+      <c r="D86" s="6">
+        <v>125</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
@@ -3886,17 +3563,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>335</v>
+      <c r="D87" s="6">
+        <v>300</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>93</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
@@ -3910,17 +3587,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>355</v>
+      <c r="D88" s="6">
+        <v>140</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>94</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
@@ -3934,17 +3611,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>343</v>
+      <c r="D89" s="6">
+        <v>50</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>95</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
@@ -3958,17 +3635,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>335</v>
+      <c r="D90" s="6">
+        <v>300</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>96</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
@@ -3982,17 +3659,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>360</v>
+      <c r="D91" s="6">
+        <v>800</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>97</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
@@ -4006,17 +3683,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D92" s="3" t="s">
-        <v>335</v>
+      <c r="D92" s="6">
+        <v>300</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
@@ -4030,17 +3707,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D93" s="3" t="s">
-        <v>335</v>
+      <c r="D93" s="6">
+        <v>300</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>99</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
@@ -4054,17 +3731,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>335</v>
+      <c r="D94" s="6">
+        <v>300</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
@@ -4078,17 +3755,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>335</v>
+      <c r="D95" s="6">
+        <v>300</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>101</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
@@ -4102,17 +3779,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>347</v>
+      <c r="D96" s="6">
+        <v>255</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>102</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
@@ -4126,17 +3803,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>361</v>
+      <c r="D97" s="6">
+        <v>54</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>103</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
@@ -4150,17 +3827,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>362</v>
+      <c r="D98" s="6">
+        <v>25</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>104</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>432</v>
+        <v>322</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
@@ -4174,17 +3851,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D99" s="3" t="s">
-        <v>339</v>
+      <c r="D99" s="6">
+        <v>100</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>105</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>432</v>
+        <v>322</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
@@ -4198,17 +3875,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>333</v>
+      <c r="D100" s="6">
+        <v>500</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>106</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>436</v>
+        <v>326</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
@@ -4222,17 +3899,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>332</v>
+      <c r="D101" s="6">
+        <v>200</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>107</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
@@ -4246,17 +3923,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>335</v>
+      <c r="D102" s="6">
+        <v>300</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>108</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
@@ -4270,17 +3947,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>343</v>
+      <c r="D103" s="6">
+        <v>50</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>109</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
@@ -4294,17 +3971,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D104" s="3" t="s">
-        <v>349</v>
+      <c r="D104" s="6">
+        <v>52.2</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
@@ -4325,10 +4002,10 @@
         <v>111</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
@@ -4342,17 +4019,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>339</v>
+      <c r="D106" s="6">
+        <v>100</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>112</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
@@ -4366,17 +4043,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D107" s="3" t="s">
-        <v>339</v>
+      <c r="D107" s="6">
+        <v>100</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>113</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
@@ -4390,17 +4067,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D108" s="3" t="s">
-        <v>363</v>
+      <c r="D108" s="6">
+        <v>35</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>114</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
@@ -4414,17 +4091,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D109" s="3" t="s">
-        <v>363</v>
+      <c r="D109" s="6">
+        <v>35</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>115</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
@@ -4438,17 +4115,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D110" s="3" t="s">
-        <v>344</v>
+      <c r="D110" s="6">
+        <v>80</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>116</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
@@ -4462,17 +4139,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D111" s="3" t="s">
-        <v>364</v>
+      <c r="D111" s="6">
+        <v>75</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>117</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
@@ -4486,17 +4163,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D112" s="3" t="s">
-        <v>344</v>
+      <c r="D112" s="6">
+        <v>80</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
@@ -4510,17 +4187,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D113" s="3" t="s">
-        <v>365</v>
+      <c r="D113" s="6">
+        <v>250</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>119</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
@@ -4534,17 +4211,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D114" s="3" t="s">
-        <v>366</v>
+      <c r="D114" s="6">
+        <v>126</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
@@ -4558,17 +4235,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D115" s="3" t="s">
-        <v>340</v>
+      <c r="D115" s="6">
+        <v>20</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>121</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
@@ -4582,17 +4259,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D116" s="3" t="s">
-        <v>340</v>
+      <c r="D116" s="6">
+        <v>20</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>122</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
@@ -4606,17 +4283,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D117" s="3" t="s">
-        <v>366</v>
+      <c r="D117" s="6">
+        <v>126</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>123</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
@@ -4630,17 +4307,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>367</v>
+      <c r="D118" s="6">
+        <v>19.989999999999998</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>124</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
@@ -4654,17 +4331,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D119" s="3" t="s">
-        <v>368</v>
+      <c r="D119" s="6">
+        <v>18</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>125</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
@@ -4678,17 +4355,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D120" s="3" t="s">
-        <v>369</v>
+      <c r="D120" s="6">
+        <v>23</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>126</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
@@ -4702,17 +4379,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D121" s="3" t="s">
-        <v>343</v>
+      <c r="D121" s="6">
+        <v>50</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>127</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
@@ -4726,17 +4403,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D122" s="3" t="s">
-        <v>327</v>
+      <c r="D122" s="6">
+        <v>150</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>128</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
@@ -4750,17 +4427,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D123" s="3" t="s">
-        <v>370</v>
+      <c r="D123" s="6">
+        <v>70</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
@@ -4774,17 +4451,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D124" s="3" t="s">
-        <v>327</v>
+      <c r="D124" s="6">
+        <v>150</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>130</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
@@ -4798,17 +4475,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D125" s="3" t="s">
-        <v>340</v>
+      <c r="D125" s="6">
+        <v>20</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>131</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
@@ -4822,17 +4499,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D126" s="3" t="s">
-        <v>371</v>
+      <c r="D126" s="6">
+        <v>240</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>132</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
@@ -4846,17 +4523,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>343</v>
+      <c r="D127" s="6">
+        <v>50</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>133</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
@@ -4870,17 +4547,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D128" s="3" t="s">
-        <v>340</v>
+      <c r="D128" s="6">
+        <v>20</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>134</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
@@ -4894,17 +4571,17 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D129" s="3" t="s">
-        <v>355</v>
+      <c r="D129" s="6">
+        <v>140</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>135</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
@@ -4925,10 +4602,10 @@
         <v>136</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>439</v>
+        <v>329</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
@@ -4942,17 +4619,17 @@
         <f t="shared" ref="C131:C194" si="2">1/1000</f>
         <v>1E-3</v>
       </c>
-      <c r="D131" s="3" t="s">
-        <v>372</v>
+      <c r="D131" s="6">
+        <v>65</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>137</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>440</v>
+        <v>330</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
@@ -4966,17 +4643,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D132" s="3" t="s">
-        <v>328</v>
+      <c r="D132" s="6">
+        <v>30</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>138</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
@@ -4990,17 +4667,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D133" s="3" t="s">
-        <v>323</v>
+      <c r="D133" s="6">
+        <v>40</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>441</v>
+        <v>331</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
@@ -5014,17 +4691,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D134" s="3" t="s">
-        <v>343</v>
+      <c r="D134" s="6">
+        <v>50</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>140</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>441</v>
+        <v>331</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
@@ -5038,17 +4715,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D135" s="3" t="s">
-        <v>335</v>
+      <c r="D135" s="6">
+        <v>300</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>439</v>
+        <v>329</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
@@ -5062,17 +4739,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D136" s="3" t="s">
-        <v>343</v>
+      <c r="D136" s="6">
+        <v>50</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>142</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
@@ -5086,17 +4763,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D137" s="3" t="s">
-        <v>373</v>
+      <c r="D137" s="6">
+        <v>98</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>441</v>
+        <v>331</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
@@ -5110,17 +4787,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D138" s="3" t="s">
-        <v>374</v>
+      <c r="D138" s="6">
+        <v>206.6</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>144</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>441</v>
+        <v>331</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
@@ -5134,17 +4811,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D139" s="3" t="s">
-        <v>335</v>
+      <c r="D139" s="6">
+        <v>300</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>145</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
@@ -5158,17 +4835,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D140" s="3" t="s">
-        <v>339</v>
+      <c r="D140" s="6">
+        <v>100</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
@@ -5182,17 +4859,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D141" s="3" t="s">
-        <v>375</v>
+      <c r="D141" s="6">
+        <v>148</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>147</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>439</v>
+        <v>329</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
@@ -5206,17 +4883,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D142" s="3" t="s">
-        <v>376</v>
+      <c r="D142" s="6">
+        <v>12</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>148</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>439</v>
+        <v>329</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
@@ -5230,17 +4907,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D143" s="3" t="s">
-        <v>339</v>
+      <c r="D143" s="6">
+        <v>100</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>149</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
@@ -5254,17 +4931,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D144" s="3" t="s">
-        <v>377</v>
+      <c r="D144" s="6">
+        <v>15.75</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>150</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
@@ -5278,17 +4955,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D145" s="3" t="s">
-        <v>364</v>
+      <c r="D145" s="6">
+        <v>75</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>151</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
@@ -5302,17 +4979,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D146" s="3" t="s">
-        <v>343</v>
+      <c r="D146" s="6">
+        <v>50</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
@@ -5326,17 +5003,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D147" s="3" t="s">
-        <v>340</v>
+      <c r="D147" s="6">
+        <v>20</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>153</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
@@ -5350,17 +5027,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D148" s="3" t="s">
-        <v>340</v>
+      <c r="D148" s="6">
+        <v>20</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>154</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
@@ -5374,17 +5051,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D149" s="3" t="s">
-        <v>378</v>
+      <c r="D149" s="6">
+        <v>95</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>155</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
@@ -5398,17 +5075,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D150" s="3" t="s">
-        <v>379</v>
+      <c r="D150" s="6">
+        <v>19.899999999999999</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>156</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
@@ -5422,17 +5099,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D151" s="3" t="s">
-        <v>340</v>
+      <c r="D151" s="6">
+        <v>20</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>157</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
@@ -5446,17 +5123,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D152" s="3" t="s">
-        <v>380</v>
+      <c r="D152" s="6">
+        <v>126.5</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>158</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>443</v>
+        <v>333</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
@@ -5470,17 +5147,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D153" s="3" t="s">
-        <v>365</v>
+      <c r="D153" s="6">
+        <v>250</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
@@ -5494,17 +5171,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D154" s="3" t="s">
-        <v>381</v>
+      <c r="D154" s="6">
+        <v>202.4</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>160</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>443</v>
+        <v>333</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
@@ -5518,17 +5195,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D155" s="3" t="s">
-        <v>382</v>
+      <c r="D155" s="6">
+        <v>197.2</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>161</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>443</v>
+        <v>333</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
@@ -5542,17 +5219,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D156" s="3" t="s">
-        <v>383</v>
+      <c r="D156" s="6">
+        <v>77</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>162</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
@@ -5566,17 +5243,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D157" s="3" t="s">
-        <v>327</v>
+      <c r="D157" s="6">
+        <v>150</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
@@ -5590,17 +5267,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D158" s="3" t="s">
-        <v>384</v>
+      <c r="D158" s="6">
+        <v>53.9</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>164</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
@@ -5614,17 +5291,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D159" s="3" t="s">
-        <v>323</v>
+      <c r="D159" s="6">
+        <v>40</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>165</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>444</v>
+        <v>334</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
@@ -5638,17 +5315,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D160" s="3" t="s">
-        <v>340</v>
+      <c r="D160" s="6">
+        <v>20</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>166</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>444</v>
+        <v>334</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
@@ -5662,17 +5339,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D161" s="3" t="s">
-        <v>340</v>
+      <c r="D161" s="6">
+        <v>20</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>167</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>444</v>
+        <v>334</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
@@ -5686,17 +5363,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D162" s="3" t="s">
-        <v>340</v>
+      <c r="D162" s="6">
+        <v>20</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>168</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>439</v>
+        <v>329</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
@@ -5710,17 +5387,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D163" s="3" t="s">
-        <v>322</v>
+      <c r="D163" s="6">
+        <v>60</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>169</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>439</v>
+        <v>329</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
@@ -5734,17 +5411,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D164" s="3" t="s">
-        <v>339</v>
+      <c r="D164" s="6">
+        <v>100</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>170</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
@@ -5758,17 +5435,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D165" s="3" t="s">
-        <v>339</v>
+      <c r="D165" s="6">
+        <v>100</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>171</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
@@ -5782,17 +5459,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D166" s="3" t="s">
-        <v>385</v>
+      <c r="D166" s="6">
+        <v>15</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>172</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
@@ -5806,17 +5483,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D167" s="3" t="s">
-        <v>385</v>
+      <c r="D167" s="6">
+        <v>15</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>173</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
@@ -5830,17 +5507,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D168" s="3" t="s">
-        <v>328</v>
+      <c r="D168" s="6">
+        <v>30</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>174</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
@@ -5854,17 +5531,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D169" s="3" t="s">
-        <v>328</v>
+      <c r="D169" s="6">
+        <v>30</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
@@ -5878,17 +5555,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D170" s="3" t="s">
-        <v>386</v>
+      <c r="D170" s="6">
+        <v>174.8</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>176</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>444</v>
+        <v>334</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
@@ -5902,17 +5579,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D171" s="3" t="s">
-        <v>343</v>
+      <c r="D171" s="6">
+        <v>50</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>177</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>444</v>
+        <v>334</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
@@ -5926,17 +5603,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D172" s="3" t="s">
-        <v>322</v>
+      <c r="D172" s="6">
+        <v>60</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>178</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
@@ -5950,17 +5627,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D173" s="3" t="s">
-        <v>339</v>
+      <c r="D173" s="6">
+        <v>100</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>179</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
@@ -5974,17 +5651,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D174" s="3" t="s">
-        <v>344</v>
+      <c r="D174" s="6">
+        <v>80</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>180</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
@@ -5998,17 +5675,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D175" s="3" t="s">
-        <v>340</v>
+      <c r="D175" s="6">
+        <v>20</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>181</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
@@ -6022,17 +5699,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D176" s="3" t="s">
-        <v>358</v>
+      <c r="D176" s="6">
+        <v>55</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>182</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
@@ -6046,17 +5723,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D177" s="3" t="s">
-        <v>340</v>
+      <c r="D177" s="6">
+        <v>20</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>183</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
@@ -6070,17 +5747,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D178" s="3" t="s">
-        <v>340</v>
+      <c r="D178" s="6">
+        <v>20</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>184</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
@@ -6094,17 +5771,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D179" s="3" t="s">
-        <v>387</v>
+      <c r="D179" s="6">
+        <v>41</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>185</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
@@ -6118,17 +5795,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D180" s="3" t="s">
-        <v>362</v>
+      <c r="D180" s="6">
+        <v>25</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>186</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
@@ -6142,17 +5819,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D181" s="3" t="s">
-        <v>372</v>
+      <c r="D181" s="6">
+        <v>65</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>187</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
@@ -6166,17 +5843,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D182" s="3" t="s">
-        <v>343</v>
+      <c r="D182" s="6">
+        <v>50</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>188</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
@@ -6190,17 +5867,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D183" s="3" t="s">
-        <v>364</v>
+      <c r="D183" s="6">
+        <v>75</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>189</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
@@ -6214,17 +5891,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D184" s="3" t="s">
-        <v>327</v>
+      <c r="D184" s="6">
+        <v>150</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>190</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
@@ -6238,17 +5915,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D185" s="3" t="s">
-        <v>327</v>
+      <c r="D185" s="6">
+        <v>150</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>191</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
@@ -6262,17 +5939,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D186" s="3" t="s">
-        <v>332</v>
+      <c r="D186" s="6">
+        <v>200</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>192</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
@@ -6286,17 +5963,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D187" s="3" t="s">
-        <v>343</v>
+      <c r="D187" s="6">
+        <v>50</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
@@ -6310,17 +5987,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D188" s="3" t="s">
-        <v>388</v>
+      <c r="D188" s="6">
+        <v>46.8</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>194</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
@@ -6334,17 +6011,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D189" s="3" t="s">
-        <v>327</v>
+      <c r="D189" s="6">
+        <v>150</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>195</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
@@ -6358,17 +6035,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D190" s="3" t="s">
-        <v>327</v>
+      <c r="D190" s="6">
+        <v>150</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>196</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
@@ -6382,17 +6059,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D191" s="3" t="s">
-        <v>364</v>
+      <c r="D191" s="6">
+        <v>75</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>197</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
@@ -6406,17 +6083,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D192" s="3" t="s">
-        <v>340</v>
+      <c r="D192" s="6">
+        <v>20</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>198</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
@@ -6430,17 +6107,17 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D193" s="3" t="s">
-        <v>332</v>
+      <c r="D193" s="6">
+        <v>200</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>199</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
@@ -6461,10 +6138,10 @@
         <v>200</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
@@ -6485,10 +6162,10 @@
         <v>201</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>447</v>
+        <v>337</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
@@ -6502,17 +6179,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D196" s="3" t="s">
-        <v>389</v>
+      <c r="D196" s="6">
+        <v>127</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>202</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
@@ -6526,17 +6203,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D197" s="3" t="s">
-        <v>390</v>
+      <c r="D197" s="6">
+        <v>53</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>203</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
@@ -6550,17 +6227,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D198" s="3" t="s">
-        <v>322</v>
+      <c r="D198" s="6">
+        <v>60</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>204</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
@@ -6568,23 +6245,23 @@
         <v>205</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>430</v>
+        <v>320</v>
       </c>
       <c r="C199">
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D199" s="3" t="s">
-        <v>391</v>
+      <c r="D199" s="6">
+        <v>569</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>205</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
@@ -6598,17 +6275,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D200" s="3" t="s">
-        <v>364</v>
+      <c r="D200" s="6">
+        <v>75</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>206</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
@@ -6622,17 +6299,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D201" s="3" t="s">
-        <v>392</v>
+      <c r="D201" s="6">
+        <v>122</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>207</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
@@ -6646,17 +6323,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D202" s="3" t="s">
-        <v>393</v>
+      <c r="D202" s="6">
+        <v>314</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>208</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
@@ -6670,17 +6347,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D203" s="3" t="s">
-        <v>394</v>
+      <c r="D203" s="6">
+        <v>74.5</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
@@ -6694,17 +6371,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D204" s="3" t="s">
-        <v>340</v>
+      <c r="D204" s="6">
+        <v>20</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>210</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
@@ -6718,17 +6395,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D205" s="3" t="s">
-        <v>370</v>
+      <c r="D205" s="6">
+        <v>70</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>211</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
@@ -6742,17 +6419,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D206" s="3" t="s">
-        <v>395</v>
+      <c r="D206" s="6">
+        <v>127.86</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>212</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
@@ -6766,17 +6443,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D207" s="3" t="s">
-        <v>396</v>
+      <c r="D207" s="6">
+        <v>130</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>213</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
@@ -6797,10 +6474,10 @@
         <v>214</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
@@ -6814,17 +6491,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D209" s="3" t="s">
-        <v>327</v>
+      <c r="D209" s="6">
+        <v>150</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>215</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
@@ -6838,17 +6515,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D210" s="3" t="s">
-        <v>397</v>
+      <c r="D210" s="6">
+        <v>82.5</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>216</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
@@ -6862,17 +6539,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D211" s="3" t="s">
-        <v>368</v>
+      <c r="D211" s="6">
+        <v>18</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>217</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
@@ -6886,17 +6563,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D212" s="3" t="s">
-        <v>364</v>
+      <c r="D212" s="6">
+        <v>75</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>218</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
@@ -6910,17 +6587,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D213" s="3" t="s">
-        <v>327</v>
+      <c r="D213" s="6">
+        <v>150</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>219</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
@@ -6934,17 +6611,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D214" s="3" t="s">
-        <v>337</v>
+      <c r="D214" s="6">
+        <v>90</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>220</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
@@ -6958,17 +6635,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D215" s="3" t="s">
-        <v>398</v>
+      <c r="D215" s="6">
+        <v>36</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>221</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
@@ -6982,17 +6659,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D216" s="3" t="s">
-        <v>344</v>
+      <c r="D216" s="6">
+        <v>80</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>222</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
@@ -7006,17 +6683,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D217" s="3" t="s">
-        <v>333</v>
+      <c r="D217" s="6">
+        <v>500</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>223</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
@@ -7030,17 +6707,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D218" s="3" t="s">
-        <v>399</v>
+      <c r="D218" s="6">
+        <v>72</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>224</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
@@ -7054,17 +6731,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D219" s="3" t="s">
-        <v>361</v>
+      <c r="D219" s="6">
+        <v>54</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>225</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
@@ -7078,17 +6755,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D220" s="3" t="s">
-        <v>339</v>
+      <c r="D220" s="6">
+        <v>100</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>226</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
@@ -7102,17 +6779,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D221" s="3" t="s">
-        <v>339</v>
+      <c r="D221" s="6">
+        <v>100</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>227</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
@@ -7126,17 +6803,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D222" s="3" t="s">
-        <v>328</v>
+      <c r="D222" s="6">
+        <v>30</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>228</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
@@ -7150,17 +6827,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D223" s="3" t="s">
-        <v>370</v>
+      <c r="D223" s="6">
+        <v>70</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>229</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
@@ -7174,17 +6851,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D224" s="3" t="s">
-        <v>400</v>
+      <c r="D224" s="6">
+        <v>63</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>230</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
@@ -7198,17 +6875,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D225" s="3" t="s">
-        <v>401</v>
+      <c r="D225" s="6">
+        <v>94</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>231</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
@@ -7222,17 +6899,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D226" s="3" t="s">
-        <v>327</v>
+      <c r="D226" s="6">
+        <v>150</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>232</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
@@ -7246,17 +6923,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D227" s="3" t="s">
-        <v>402</v>
+      <c r="D227" s="6">
+        <v>117</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>233</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
@@ -7270,17 +6947,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D228" s="3" t="s">
-        <v>340</v>
+      <c r="D228" s="6">
+        <v>20</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>234</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
@@ -7294,17 +6971,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D229" s="3" t="s">
-        <v>337</v>
+      <c r="D229" s="6">
+        <v>90</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>235</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
@@ -7318,17 +6995,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D230" s="3" t="s">
-        <v>403</v>
+      <c r="D230" s="6">
+        <v>107</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>236</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
@@ -7342,17 +7019,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D231" s="3" t="s">
-        <v>404</v>
+      <c r="D231" s="6">
+        <v>118.56</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>237</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
@@ -7366,17 +7043,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D232" s="3" t="s">
-        <v>364</v>
+      <c r="D232" s="6">
+        <v>75</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
@@ -7390,17 +7067,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D233" s="3" t="s">
-        <v>364</v>
+      <c r="D233" s="6">
+        <v>75</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>239</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
@@ -7414,17 +7091,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D234" s="3" t="s">
-        <v>405</v>
+      <c r="D234" s="6">
+        <v>26</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>240</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
@@ -7438,17 +7115,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D235" s="3" t="s">
-        <v>405</v>
+      <c r="D235" s="6">
+        <v>26</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>241</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
@@ -7462,17 +7139,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D236" s="3" t="s">
-        <v>337</v>
+      <c r="D236" s="6">
+        <v>90</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>242</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
@@ -7486,17 +7163,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D237" s="3" t="s">
-        <v>327</v>
+      <c r="D237" s="6">
+        <v>150</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>243</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
@@ -7510,17 +7187,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D238" s="3" t="s">
-        <v>340</v>
+      <c r="D238" s="6">
+        <v>20</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>244</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
@@ -7534,17 +7211,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D239" s="3" t="s">
-        <v>385</v>
+      <c r="D239" s="6">
+        <v>15</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>245</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
@@ -7558,17 +7235,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D240" s="3" t="s">
-        <v>385</v>
+      <c r="D240" s="6">
+        <v>15</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>246</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
@@ -7582,17 +7259,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D241" s="3" t="s">
-        <v>385</v>
+      <c r="D241" s="6">
+        <v>15</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>247</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
@@ -7606,17 +7283,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D242" s="3" t="s">
-        <v>406</v>
+      <c r="D242" s="6">
+        <v>10</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>248</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
@@ -7630,17 +7307,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D243" s="3" t="s">
-        <v>327</v>
+      <c r="D243" s="6">
+        <v>150</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>249</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
@@ -7661,10 +7338,10 @@
         <v>250</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
@@ -7678,17 +7355,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D245" s="3" t="s">
-        <v>344</v>
+      <c r="D245" s="6">
+        <v>80</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>251</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
@@ -7702,17 +7379,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D246" s="3" t="s">
-        <v>340</v>
+      <c r="D246" s="6">
+        <v>20</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>252</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
@@ -7726,17 +7403,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D247" s="3" t="s">
-        <v>322</v>
+      <c r="D247" s="6">
+        <v>60</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>253</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
@@ -7750,17 +7427,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D248" s="3" t="s">
-        <v>407</v>
+      <c r="D248" s="6">
+        <v>102</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>254</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
@@ -7774,17 +7451,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D249" s="3" t="s">
-        <v>364</v>
+      <c r="D249" s="6">
+        <v>75</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>255</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
@@ -7798,17 +7475,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D250" s="3" t="s">
-        <v>343</v>
+      <c r="D250" s="6">
+        <v>50</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>256</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
@@ -7822,17 +7499,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D251" s="3" t="s">
-        <v>327</v>
+      <c r="D251" s="6">
+        <v>150</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>257</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
@@ -7846,17 +7523,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D252" s="3" t="s">
-        <v>364</v>
+      <c r="D252" s="6">
+        <v>75</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>258</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
@@ -7870,17 +7547,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D253" s="3" t="s">
-        <v>408</v>
+      <c r="D253" s="6">
+        <v>62</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>259</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
@@ -7894,17 +7571,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D254" s="3" t="s">
-        <v>322</v>
+      <c r="D254" s="6">
+        <v>60</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>260</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
@@ -7918,17 +7595,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D255" s="3" t="s">
-        <v>339</v>
+      <c r="D255" s="6">
+        <v>100</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>261</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
@@ -7942,17 +7619,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D256" s="3" t="s">
-        <v>339</v>
+      <c r="D256" s="6">
+        <v>100</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>262</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
@@ -7966,17 +7643,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D257" s="3" t="s">
-        <v>340</v>
+      <c r="D257" s="6">
+        <v>20</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>263</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
@@ -7990,17 +7667,17 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D258" s="3" t="s">
-        <v>409</v>
+      <c r="D258" s="6">
+        <v>62.5</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>264</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
@@ -8014,17 +7691,17 @@
         <f t="shared" ref="C259:C312" si="4">1/1000</f>
         <v>1E-3</v>
       </c>
-      <c r="D259" s="3" t="s">
-        <v>410</v>
+      <c r="D259" s="6">
+        <v>14.2</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>265</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
@@ -8038,17 +7715,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D260" s="3" t="s">
-        <v>411</v>
+      <c r="D260" s="6">
+        <v>128</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>266</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
@@ -8062,17 +7739,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D261" s="3" t="s">
-        <v>412</v>
+      <c r="D261" s="6">
+        <v>160</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>267</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
@@ -8086,17 +7763,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D262" s="3" t="s">
-        <v>340</v>
+      <c r="D262" s="6">
+        <v>20</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>268</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
@@ -8110,17 +7787,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D263" s="3" t="s">
-        <v>327</v>
+      <c r="D263" s="6">
+        <v>150</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
@@ -8134,17 +7811,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D264" s="3" t="s">
-        <v>327</v>
+      <c r="D264" s="6">
+        <v>150</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>270</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
@@ -8158,17 +7835,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D265" s="3" t="s">
-        <v>333</v>
+      <c r="D265" s="6">
+        <v>500</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>271</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
@@ -8182,17 +7859,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D266" s="3" t="s">
-        <v>343</v>
+      <c r="D266" s="6">
+        <v>50</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>272</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
@@ -8213,10 +7890,10 @@
         <v>273</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
@@ -8237,10 +7914,10 @@
         <v>274</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
@@ -8254,17 +7931,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D269" s="3" t="s">
-        <v>413</v>
+      <c r="D269" s="6">
+        <v>127.5</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>275</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
@@ -8278,17 +7955,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D270" s="3" t="s">
-        <v>339</v>
+      <c r="D270" s="6">
+        <v>100</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>276</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
@@ -8302,17 +7979,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D271" s="3" t="s">
-        <v>339</v>
+      <c r="D271" s="6">
+        <v>100</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>277</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
@@ -8320,122 +7997,122 @@
         <v>278</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>429</v>
+        <v>319</v>
       </c>
       <c r="C272">
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D272" s="3" t="s">
-        <v>414</v>
+      <c r="D272" s="6">
+        <v>833</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>278</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>279</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>429</v>
+        <v>319</v>
       </c>
       <c r="C273">
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D273" s="3" t="s">
-        <v>415</v>
+      <c r="D273" s="6">
+        <v>836</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>279</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>280</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>429</v>
+        <v>319</v>
       </c>
       <c r="C274">
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D274" s="3" t="s">
-        <v>416</v>
+      <c r="D274" s="6">
+        <v>820</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>280</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>281</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>429</v>
+        <v>319</v>
       </c>
       <c r="C275">
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D275" s="3" t="s">
-        <v>417</v>
+      <c r="D275" s="6">
+        <v>800.1</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>281</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>282</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>429</v>
+        <v>319</v>
       </c>
       <c r="C276">
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D276" s="3" t="s">
-        <v>417</v>
+      <c r="D276" s="6">
+        <v>800.1</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>282</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>283</v>
       </c>
@@ -8446,20 +8123,20 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D277" s="3" t="s">
-        <v>364</v>
+      <c r="D277" s="6">
+        <v>75</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>283</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>284</v>
       </c>
@@ -8470,20 +8147,24 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D278" s="3" t="s">
-        <v>418</v>
+      <c r="D278" s="6">
+        <v>79</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>284</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>434</v>
+        <v>324</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+      <c r="H278" s="5">
+        <f>SUM(D:D)</f>
+        <v>40783.17</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>285</v>
       </c>
@@ -8494,20 +8175,20 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D279" s="3" t="s">
-        <v>351</v>
+      <c r="D279" s="6">
+        <v>260</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>285</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>286</v>
       </c>
@@ -8518,20 +8199,20 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D280" s="3" t="s">
-        <v>337</v>
+      <c r="D280" s="6">
+        <v>90</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>286</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>287</v>
       </c>
@@ -8542,20 +8223,20 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D281" s="3" t="s">
-        <v>365</v>
+      <c r="D281" s="6">
+        <v>250</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>287</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>288</v>
       </c>
@@ -8566,20 +8247,20 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D282" s="3" t="s">
-        <v>419</v>
+      <c r="D282" s="6">
+        <v>167</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>288</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>289</v>
       </c>
@@ -8590,20 +8271,20 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D283" s="3" t="s">
-        <v>340</v>
+      <c r="D283" s="6">
+        <v>20</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>289</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>290</v>
       </c>
@@ -8614,20 +8295,20 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D284" s="3" t="s">
-        <v>340</v>
+      <c r="D284" s="6">
+        <v>20</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>290</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>291</v>
       </c>
@@ -8638,20 +8319,20 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D285" s="3" t="s">
-        <v>340</v>
+      <c r="D285" s="6">
+        <v>20</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>291</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>292</v>
       </c>
@@ -8662,20 +8343,20 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D286" s="3" t="s">
-        <v>359</v>
+      <c r="D286" s="6">
+        <v>125</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>292</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>293</v>
       </c>
@@ -8693,13 +8374,13 @@
         <v>293</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>294</v>
       </c>
@@ -8710,17 +8391,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D288" s="3" t="s">
-        <v>327</v>
+      <c r="D288" s="6">
+        <v>150</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>294</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
@@ -8734,17 +8415,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D289" s="3" t="s">
-        <v>340</v>
+      <c r="D289" s="6">
+        <v>20</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
@@ -8758,17 +8439,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D290" s="3" t="s">
-        <v>344</v>
+      <c r="D290" s="6">
+        <v>80</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>296</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
@@ -8782,17 +8463,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D291" s="3" t="s">
-        <v>420</v>
+      <c r="D291" s="6">
+        <v>188.5</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>297</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.35">
@@ -8806,17 +8487,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D292" s="3" t="s">
-        <v>421</v>
+      <c r="D292" s="6">
+        <v>45</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>298</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.35">
@@ -8830,17 +8511,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D293" s="3" t="s">
-        <v>358</v>
+      <c r="D293" s="6">
+        <v>55</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>299</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.35">
@@ -8854,17 +8535,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D294" s="3" t="s">
-        <v>343</v>
+      <c r="D294" s="6">
+        <v>50</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>300</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.35">
@@ -8878,17 +8559,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D295" s="3" t="s">
-        <v>332</v>
+      <c r="D295" s="6">
+        <v>200</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>301</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.35">
@@ -8902,17 +8583,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D296" s="3" t="s">
-        <v>422</v>
+      <c r="D296" s="6">
+        <v>106</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>302</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.35">
@@ -8926,17 +8607,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D297" s="3" t="s">
-        <v>372</v>
+      <c r="D297" s="6">
+        <v>65</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>303</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.35">
@@ -8950,17 +8631,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D298" s="3" t="s">
-        <v>337</v>
+      <c r="D298" s="6">
+        <v>90</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>304</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.35">
@@ -8974,17 +8655,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D299" s="3" t="s">
-        <v>339</v>
+      <c r="D299" s="6">
+        <v>100</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>305</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.35">
@@ -8998,17 +8679,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D300" s="3" t="s">
-        <v>365</v>
+      <c r="D300" s="6">
+        <v>250</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>306</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
@@ -9022,17 +8703,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D301" s="3" t="s">
-        <v>423</v>
+      <c r="D301" s="6">
+        <v>225</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>307</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.35">
@@ -9046,17 +8727,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D302" s="3" t="s">
-        <v>424</v>
+      <c r="D302" s="6">
+        <v>222</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>308</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.35">
@@ -9070,17 +8751,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D303" s="3" t="s">
-        <v>327</v>
+      <c r="D303" s="6">
+        <v>150</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>309</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.35">
@@ -9094,17 +8775,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D304" s="3" t="s">
-        <v>343</v>
+      <c r="D304" s="6">
+        <v>50</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>310</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.35">
@@ -9118,17 +8799,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D305" s="3" t="s">
-        <v>319</v>
+      <c r="D305" s="6">
+        <v>120</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>311</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.35">
@@ -9142,17 +8823,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D306" s="3" t="s">
-        <v>425</v>
+      <c r="D306" s="6">
+        <v>82</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>312</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.35">
@@ -9166,17 +8847,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D307" s="3" t="s">
-        <v>370</v>
+      <c r="D307" s="6">
+        <v>70</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>313</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.35">
@@ -9190,17 +8871,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D308" s="3" t="s">
-        <v>426</v>
+      <c r="D308" s="6">
+        <v>57</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>314</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.35">
@@ -9214,17 +8895,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D309" s="3" t="s">
-        <v>427</v>
+      <c r="D309" s="6">
+        <v>22</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>315</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.35">
@@ -9238,17 +8919,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D310" s="3" t="s">
-        <v>373</v>
+      <c r="D310" s="6">
+        <v>98</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>316</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.35">
@@ -9262,17 +8943,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D311" s="3" t="s">
-        <v>428</v>
+      <c r="D311" s="6">
+        <v>64.2</v>
       </c>
       <c r="E311" s="2" t="s">
         <v>317</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.35">
@@ -9286,17 +8967,17 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D312" s="3" t="s">
-        <v>319</v>
+      <c r="D312" s="6">
+        <v>120</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>318</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>446</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/Thesis/developer_states.xlsx
+++ b/Thesis/developer_states.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/abigail_weeks_rmi_org/Documents/Documents/GitHub/Thesis/Thesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="264" documentId="8_{A4B64DE1-C1F9-4DF8-A805-E80C52345F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F45BABC-6B5F-470E-96B2-DA3D3AFCA013}"/>
+  <xr:revisionPtr revIDLastSave="282" documentId="8_{A4B64DE1-C1F9-4DF8-A805-E80C52345F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F86A9FB0-9B2C-4488-9B0C-34D92477D784}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{31558D2F-F994-4500-BC80-1C41F5323AB0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31558D2F-F994-4500-BC80-1C41F5323AB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1119,7 +1119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1134,9 +1134,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1483,6 +1480,7 @@
     <col min="3" max="3" width="18.54296875" customWidth="1"/>
     <col min="4" max="4" width="8.7265625" style="5"/>
     <col min="5" max="5" width="12.7265625" customWidth="1"/>
+    <col min="8" max="8" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -1519,7 +1517,7 @@
         <f>1/1000</f>
         <v>1E-3</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="2">
         <v>120</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -1543,7 +1541,7 @@
         <f t="shared" ref="C3:C66" si="0">1/1000</f>
         <v>1E-3</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="2">
         <v>109.3</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -1567,7 +1565,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="2">
         <v>440</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -1591,7 +1589,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="2">
         <v>440</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -1615,7 +1613,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="2">
         <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -1639,7 +1637,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="2">
         <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -1663,7 +1661,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="2">
         <v>8.4</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -1675,9 +1673,9 @@
       <c r="G8" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="I8" s="5">
-        <f>SUM(D:D)</f>
-        <v>40783.17</v>
+      <c r="I8" s="5" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -1691,7 +1689,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="2">
         <v>18.149999999999999</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -1715,7 +1713,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="2">
         <v>294.7</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -1739,7 +1737,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="2">
         <v>150</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -1763,7 +1761,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="2">
         <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -1787,7 +1785,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="2">
         <v>299</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -1811,7 +1809,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="2">
         <v>62.4</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -1835,7 +1833,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="2">
         <v>43.2</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -1859,7 +1857,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="2">
         <v>200</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -1883,7 +1881,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="2">
         <v>500</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -1907,7 +1905,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="2">
         <v>95.1</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -1931,7 +1929,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="2">
         <v>300</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -1955,7 +1953,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="2">
         <v>300</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -1979,7 +1977,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="2">
         <v>118.6</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -2003,7 +2001,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="2">
         <v>200</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -2027,7 +2025,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="2">
         <v>90</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -2051,7 +2049,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="2">
         <v>144</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -2075,7 +2073,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="2">
         <v>100</v>
       </c>
       <c r="E25" s="2" t="s">
@@ -2099,7 +2097,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="2">
         <v>20</v>
       </c>
       <c r="E26" s="2" t="s">
@@ -2123,7 +2121,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="2">
         <v>42.2</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -2147,7 +2145,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="2">
         <v>20</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -2171,7 +2169,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="2">
         <v>150</v>
       </c>
       <c r="E29" s="2" t="s">
@@ -2195,7 +2193,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="2">
         <v>100</v>
       </c>
       <c r="E30" s="2" t="s">
@@ -2219,7 +2217,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="2">
         <v>79.5</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -2243,7 +2241,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="2">
         <v>150</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -2267,7 +2265,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="2">
         <v>150</v>
       </c>
       <c r="E33" s="2" t="s">
@@ -2291,7 +2289,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="2">
         <v>50</v>
       </c>
       <c r="E34" s="2" t="s">
@@ -2315,7 +2313,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="2">
         <v>50</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -2339,7 +2337,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="2">
         <v>300</v>
       </c>
       <c r="E36" s="2" t="s">
@@ -2363,7 +2361,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="2">
         <v>80</v>
       </c>
       <c r="E37" s="2" t="s">
@@ -2387,7 +2385,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="2">
         <v>199</v>
       </c>
       <c r="E38" s="2" t="s">
@@ -2411,7 +2409,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="2">
         <v>100</v>
       </c>
       <c r="E39" s="2" t="s">
@@ -2435,7 +2433,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="2">
         <v>200</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -2459,7 +2457,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="2">
         <v>300</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -2483,7 +2481,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="2">
         <v>200</v>
       </c>
       <c r="E42" s="2" t="s">
@@ -2507,7 +2505,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="2">
         <v>20</v>
       </c>
       <c r="E43" s="2" t="s">
@@ -2531,7 +2529,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="2">
         <v>175</v>
       </c>
       <c r="E44" s="2" t="s">
@@ -2603,7 +2601,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="2">
         <v>200</v>
       </c>
       <c r="E47" s="2" t="s">
@@ -2627,7 +2625,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="2">
         <v>255</v>
       </c>
       <c r="E48" s="2" t="s">
@@ -2651,7 +2649,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="2">
         <v>180</v>
       </c>
       <c r="E49" s="2" t="s">
@@ -2675,7 +2673,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="2">
         <v>52.2</v>
       </c>
       <c r="E50" s="2" t="s">
@@ -2699,7 +2697,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="2">
         <v>100</v>
       </c>
       <c r="E51" s="2" t="s">
@@ -2723,7 +2721,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="2">
         <v>300</v>
       </c>
       <c r="E52" s="2" t="s">
@@ -2747,7 +2745,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="2">
         <v>150</v>
       </c>
       <c r="E53" s="2" t="s">
@@ -2771,7 +2769,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="2">
         <v>150</v>
       </c>
       <c r="E54" s="2" t="s">
@@ -2795,7 +2793,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="2">
         <v>50</v>
       </c>
       <c r="E55" s="2" t="s">
@@ -2819,7 +2817,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="2">
         <v>300</v>
       </c>
       <c r="E56" s="2" t="s">
@@ -2843,7 +2841,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="2">
         <v>300</v>
       </c>
       <c r="E57" s="2" t="s">
@@ -2867,7 +2865,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="2">
         <v>150</v>
       </c>
       <c r="E58" s="2" t="s">
@@ -2891,7 +2889,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59" s="2">
         <v>150</v>
       </c>
       <c r="E59" s="2" t="s">
@@ -2915,7 +2913,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60" s="2">
         <v>100</v>
       </c>
       <c r="E60" s="2" t="s">
@@ -2939,7 +2937,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="2">
         <v>150</v>
       </c>
       <c r="E61" s="2" t="s">
@@ -2963,7 +2961,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D62" s="2">
         <v>299.97000000000003</v>
       </c>
       <c r="E62" s="2" t="s">
@@ -2987,7 +2985,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D63" s="2">
         <v>260</v>
       </c>
       <c r="E63" s="2" t="s">
@@ -3011,7 +3009,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64" s="2">
         <v>212</v>
       </c>
       <c r="E64" s="2" t="s">
@@ -3035,7 +3033,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65" s="2">
         <v>200</v>
       </c>
       <c r="E65" s="2" t="s">
@@ -3059,7 +3057,7 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66" s="2">
         <v>255</v>
       </c>
       <c r="E66" s="2" t="s">
@@ -3083,7 +3081,7 @@
         <f t="shared" ref="C67:C130" si="1">1/1000</f>
         <v>1E-3</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D67" s="2">
         <v>190.89</v>
       </c>
       <c r="E67" s="2" t="s">
@@ -3131,7 +3129,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D69" s="2">
         <v>300</v>
       </c>
       <c r="E69" s="2" t="s">
@@ -3155,7 +3153,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D70" s="6">
+      <c r="D70" s="2">
         <v>200</v>
       </c>
       <c r="E70" s="2" t="s">
@@ -3179,7 +3177,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D71" s="6">
+      <c r="D71" s="2">
         <v>346</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -3203,7 +3201,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D72" s="2">
         <v>100</v>
       </c>
       <c r="E72" s="2" t="s">
@@ -3227,7 +3225,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D73" s="6">
+      <c r="D73" s="2">
         <v>100</v>
       </c>
       <c r="E73" s="2" t="s">
@@ -3251,7 +3249,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D74" s="6">
+      <c r="D74" s="2">
         <v>100</v>
       </c>
       <c r="E74" s="2" t="s">
@@ -3275,7 +3273,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D75" s="2">
         <v>150</v>
       </c>
       <c r="E75" s="2" t="s">
@@ -3299,7 +3297,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D76" s="6">
+      <c r="D76" s="2">
         <v>200</v>
       </c>
       <c r="E76" s="2" t="s">
@@ -3323,7 +3321,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D77" s="6">
+      <c r="D77" s="2">
         <v>200</v>
       </c>
       <c r="E77" s="2" t="s">
@@ -3371,7 +3369,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D79" s="6">
+      <c r="D79" s="2">
         <v>100</v>
       </c>
       <c r="E79" s="2" t="s">
@@ -3395,7 +3393,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D80" s="6">
+      <c r="D80" s="2">
         <v>140</v>
       </c>
       <c r="E80" s="2" t="s">
@@ -3419,7 +3417,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D81" s="6">
+      <c r="D81" s="2">
         <v>100</v>
       </c>
       <c r="E81" s="2" t="s">
@@ -3443,7 +3441,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D82" s="6">
+      <c r="D82" s="2">
         <v>210</v>
       </c>
       <c r="E82" s="2" t="s">
@@ -3467,7 +3465,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D83" s="6">
+      <c r="D83" s="2">
         <v>450</v>
       </c>
       <c r="E83" s="2" t="s">
@@ -3491,7 +3489,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D84" s="6">
+      <c r="D84" s="2">
         <v>180</v>
       </c>
       <c r="E84" s="2" t="s">
@@ -3515,7 +3513,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D85" s="6">
+      <c r="D85" s="2">
         <v>55</v>
       </c>
       <c r="E85" s="2" t="s">
@@ -3539,7 +3537,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D86" s="6">
+      <c r="D86" s="2">
         <v>125</v>
       </c>
       <c r="E86" s="2" t="s">
@@ -3563,7 +3561,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D87" s="6">
+      <c r="D87" s="2">
         <v>300</v>
       </c>
       <c r="E87" s="2" t="s">
@@ -3587,7 +3585,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D88" s="6">
+      <c r="D88" s="2">
         <v>140</v>
       </c>
       <c r="E88" s="2" t="s">
@@ -3611,7 +3609,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D89" s="6">
+      <c r="D89" s="2">
         <v>50</v>
       </c>
       <c r="E89" s="2" t="s">
@@ -3635,7 +3633,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D90" s="6">
+      <c r="D90" s="2">
         <v>300</v>
       </c>
       <c r="E90" s="2" t="s">
@@ -3659,7 +3657,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D91" s="6">
+      <c r="D91" s="2">
         <v>800</v>
       </c>
       <c r="E91" s="2" t="s">
@@ -3683,7 +3681,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D92" s="6">
+      <c r="D92" s="2">
         <v>300</v>
       </c>
       <c r="E92" s="2" t="s">
@@ -3707,7 +3705,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D93" s="6">
+      <c r="D93" s="2">
         <v>300</v>
       </c>
       <c r="E93" s="2" t="s">
@@ -3731,7 +3729,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D94" s="6">
+      <c r="D94" s="2">
         <v>300</v>
       </c>
       <c r="E94" s="2" t="s">
@@ -3755,7 +3753,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D95" s="6">
+      <c r="D95" s="2">
         <v>300</v>
       </c>
       <c r="E95" s="2" t="s">
@@ -3779,7 +3777,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D96" s="6">
+      <c r="D96" s="2">
         <v>255</v>
       </c>
       <c r="E96" s="2" t="s">
@@ -3803,7 +3801,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D97" s="6">
+      <c r="D97" s="2">
         <v>54</v>
       </c>
       <c r="E97" s="2" t="s">
@@ -3827,7 +3825,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D98" s="6">
+      <c r="D98" s="2">
         <v>25</v>
       </c>
       <c r="E98" s="2" t="s">
@@ -3851,7 +3849,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D99" s="6">
+      <c r="D99" s="2">
         <v>100</v>
       </c>
       <c r="E99" s="2" t="s">
@@ -3875,7 +3873,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D100" s="6">
+      <c r="D100" s="2">
         <v>500</v>
       </c>
       <c r="E100" s="2" t="s">
@@ -3899,7 +3897,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D101" s="6">
+      <c r="D101" s="2">
         <v>200</v>
       </c>
       <c r="E101" s="2" t="s">
@@ -3923,7 +3921,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D102" s="6">
+      <c r="D102" s="2">
         <v>300</v>
       </c>
       <c r="E102" s="2" t="s">
@@ -3947,7 +3945,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D103" s="6">
+      <c r="D103" s="2">
         <v>50</v>
       </c>
       <c r="E103" s="2" t="s">
@@ -3971,7 +3969,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D104" s="6">
+      <c r="D104" s="2">
         <v>52.2</v>
       </c>
       <c r="E104" s="2" t="s">
@@ -4019,7 +4017,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D106" s="6">
+      <c r="D106" s="2">
         <v>100</v>
       </c>
       <c r="E106" s="2" t="s">
@@ -4043,7 +4041,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D107" s="6">
+      <c r="D107" s="2">
         <v>100</v>
       </c>
       <c r="E107" s="2" t="s">
@@ -4067,7 +4065,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D108" s="6">
+      <c r="D108" s="2">
         <v>35</v>
       </c>
       <c r="E108" s="2" t="s">
@@ -4091,7 +4089,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D109" s="6">
+      <c r="D109" s="2">
         <v>35</v>
       </c>
       <c r="E109" s="2" t="s">
@@ -4115,7 +4113,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D110" s="6">
+      <c r="D110" s="2">
         <v>80</v>
       </c>
       <c r="E110" s="2" t="s">
@@ -4139,7 +4137,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D111" s="6">
+      <c r="D111" s="2">
         <v>75</v>
       </c>
       <c r="E111" s="2" t="s">
@@ -4163,7 +4161,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D112" s="6">
+      <c r="D112" s="2">
         <v>80</v>
       </c>
       <c r="E112" s="2" t="s">
@@ -4187,7 +4185,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D113" s="6">
+      <c r="D113" s="2">
         <v>250</v>
       </c>
       <c r="E113" s="2" t="s">
@@ -4211,7 +4209,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D114" s="6">
+      <c r="D114" s="2">
         <v>126</v>
       </c>
       <c r="E114" s="2" t="s">
@@ -4235,7 +4233,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D115" s="6">
+      <c r="D115" s="2">
         <v>20</v>
       </c>
       <c r="E115" s="2" t="s">
@@ -4259,7 +4257,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D116" s="6">
+      <c r="D116" s="2">
         <v>20</v>
       </c>
       <c r="E116" s="2" t="s">
@@ -4283,7 +4281,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D117" s="6">
+      <c r="D117" s="2">
         <v>126</v>
       </c>
       <c r="E117" s="2" t="s">
@@ -4307,7 +4305,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D118" s="6">
+      <c r="D118" s="2">
         <v>19.989999999999998</v>
       </c>
       <c r="E118" s="2" t="s">
@@ -4331,7 +4329,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D119" s="6">
+      <c r="D119" s="2">
         <v>18</v>
       </c>
       <c r="E119" s="2" t="s">
@@ -4355,7 +4353,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D120" s="6">
+      <c r="D120" s="2">
         <v>23</v>
       </c>
       <c r="E120" s="2" t="s">
@@ -4379,7 +4377,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D121" s="6">
+      <c r="D121" s="2">
         <v>50</v>
       </c>
       <c r="E121" s="2" t="s">
@@ -4403,7 +4401,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D122" s="6">
+      <c r="D122" s="2">
         <v>150</v>
       </c>
       <c r="E122" s="2" t="s">
@@ -4427,7 +4425,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D123" s="6">
+      <c r="D123" s="2">
         <v>70</v>
       </c>
       <c r="E123" s="2" t="s">
@@ -4451,7 +4449,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D124" s="6">
+      <c r="D124" s="2">
         <v>150</v>
       </c>
       <c r="E124" s="2" t="s">
@@ -4475,7 +4473,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D125" s="6">
+      <c r="D125" s="2">
         <v>20</v>
       </c>
       <c r="E125" s="2" t="s">
@@ -4499,7 +4497,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D126" s="6">
+      <c r="D126" s="2">
         <v>240</v>
       </c>
       <c r="E126" s="2" t="s">
@@ -4523,7 +4521,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D127" s="6">
+      <c r="D127" s="2">
         <v>50</v>
       </c>
       <c r="E127" s="2" t="s">
@@ -4547,7 +4545,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D128" s="6">
+      <c r="D128" s="2">
         <v>20</v>
       </c>
       <c r="E128" s="2" t="s">
@@ -4571,7 +4569,7 @@
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="D129" s="6">
+      <c r="D129" s="2">
         <v>140</v>
       </c>
       <c r="E129" s="2" t="s">
@@ -4619,7 +4617,7 @@
         <f t="shared" ref="C131:C194" si="2">1/1000</f>
         <v>1E-3</v>
       </c>
-      <c r="D131" s="6">
+      <c r="D131" s="2">
         <v>65</v>
       </c>
       <c r="E131" s="2" t="s">
@@ -4643,7 +4641,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D132" s="6">
+      <c r="D132" s="2">
         <v>30</v>
       </c>
       <c r="E132" s="2" t="s">
@@ -4667,7 +4665,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D133" s="6">
+      <c r="D133" s="2">
         <v>40</v>
       </c>
       <c r="E133" s="2" t="s">
@@ -4691,7 +4689,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D134" s="6">
+      <c r="D134" s="2">
         <v>50</v>
       </c>
       <c r="E134" s="2" t="s">
@@ -4715,7 +4713,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D135" s="6">
+      <c r="D135" s="2">
         <v>300</v>
       </c>
       <c r="E135" s="2" t="s">
@@ -4739,7 +4737,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D136" s="6">
+      <c r="D136" s="2">
         <v>50</v>
       </c>
       <c r="E136" s="2" t="s">
@@ -4763,7 +4761,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D137" s="6">
+      <c r="D137" s="2">
         <v>98</v>
       </c>
       <c r="E137" s="2" t="s">
@@ -4787,7 +4785,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D138" s="6">
+      <c r="D138" s="2">
         <v>206.6</v>
       </c>
       <c r="E138" s="2" t="s">
@@ -4811,7 +4809,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D139" s="6">
+      <c r="D139" s="2">
         <v>300</v>
       </c>
       <c r="E139" s="2" t="s">
@@ -4835,7 +4833,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D140" s="6">
+      <c r="D140" s="2">
         <v>100</v>
       </c>
       <c r="E140" s="2" t="s">
@@ -4859,7 +4857,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D141" s="6">
+      <c r="D141" s="2">
         <v>148</v>
       </c>
       <c r="E141" s="2" t="s">
@@ -4883,7 +4881,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D142" s="6">
+      <c r="D142" s="2">
         <v>12</v>
       </c>
       <c r="E142" s="2" t="s">
@@ -4907,7 +4905,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D143" s="6">
+      <c r="D143" s="2">
         <v>100</v>
       </c>
       <c r="E143" s="2" t="s">
@@ -4931,7 +4929,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D144" s="6">
+      <c r="D144" s="2">
         <v>15.75</v>
       </c>
       <c r="E144" s="2" t="s">
@@ -4955,7 +4953,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D145" s="6">
+      <c r="D145" s="2">
         <v>75</v>
       </c>
       <c r="E145" s="2" t="s">
@@ -4979,7 +4977,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D146" s="6">
+      <c r="D146" s="2">
         <v>50</v>
       </c>
       <c r="E146" s="2" t="s">
@@ -5003,7 +5001,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D147" s="6">
+      <c r="D147" s="2">
         <v>20</v>
       </c>
       <c r="E147" s="2" t="s">
@@ -5027,7 +5025,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D148" s="6">
+      <c r="D148" s="2">
         <v>20</v>
       </c>
       <c r="E148" s="2" t="s">
@@ -5051,7 +5049,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D149" s="6">
+      <c r="D149" s="2">
         <v>95</v>
       </c>
       <c r="E149" s="2" t="s">
@@ -5075,7 +5073,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D150" s="6">
+      <c r="D150" s="2">
         <v>19.899999999999999</v>
       </c>
       <c r="E150" s="2" t="s">
@@ -5099,7 +5097,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D151" s="6">
+      <c r="D151" s="2">
         <v>20</v>
       </c>
       <c r="E151" s="2" t="s">
@@ -5123,7 +5121,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D152" s="6">
+      <c r="D152" s="2">
         <v>126.5</v>
       </c>
       <c r="E152" s="2" t="s">
@@ -5147,7 +5145,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D153" s="6">
+      <c r="D153" s="2">
         <v>250</v>
       </c>
       <c r="E153" s="2" t="s">
@@ -5171,7 +5169,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D154" s="6">
+      <c r="D154" s="2">
         <v>202.4</v>
       </c>
       <c r="E154" s="2" t="s">
@@ -5195,7 +5193,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D155" s="6">
+      <c r="D155" s="2">
         <v>197.2</v>
       </c>
       <c r="E155" s="2" t="s">
@@ -5219,7 +5217,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D156" s="6">
+      <c r="D156" s="2">
         <v>77</v>
       </c>
       <c r="E156" s="2" t="s">
@@ -5243,7 +5241,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D157" s="6">
+      <c r="D157" s="2">
         <v>150</v>
       </c>
       <c r="E157" s="2" t="s">
@@ -5267,7 +5265,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D158" s="6">
+      <c r="D158" s="2">
         <v>53.9</v>
       </c>
       <c r="E158" s="2" t="s">
@@ -5291,7 +5289,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D159" s="6">
+      <c r="D159" s="2">
         <v>40</v>
       </c>
       <c r="E159" s="2" t="s">
@@ -5315,7 +5313,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D160" s="6">
+      <c r="D160" s="2">
         <v>20</v>
       </c>
       <c r="E160" s="2" t="s">
@@ -5339,7 +5337,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D161" s="6">
+      <c r="D161" s="2">
         <v>20</v>
       </c>
       <c r="E161" s="2" t="s">
@@ -5363,7 +5361,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D162" s="6">
+      <c r="D162" s="2">
         <v>20</v>
       </c>
       <c r="E162" s="2" t="s">
@@ -5387,7 +5385,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D163" s="6">
+      <c r="D163" s="2">
         <v>60</v>
       </c>
       <c r="E163" s="2" t="s">
@@ -5411,7 +5409,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D164" s="6">
+      <c r="D164" s="2">
         <v>100</v>
       </c>
       <c r="E164" s="2" t="s">
@@ -5435,7 +5433,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D165" s="6">
+      <c r="D165" s="2">
         <v>100</v>
       </c>
       <c r="E165" s="2" t="s">
@@ -5459,7 +5457,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D166" s="6">
+      <c r="D166" s="2">
         <v>15</v>
       </c>
       <c r="E166" s="2" t="s">
@@ -5483,7 +5481,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D167" s="6">
+      <c r="D167" s="2">
         <v>15</v>
       </c>
       <c r="E167" s="2" t="s">
@@ -5507,7 +5505,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D168" s="6">
+      <c r="D168" s="2">
         <v>30</v>
       </c>
       <c r="E168" s="2" t="s">
@@ -5531,7 +5529,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D169" s="6">
+      <c r="D169" s="2">
         <v>30</v>
       </c>
       <c r="E169" s="2" t="s">
@@ -5555,7 +5553,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D170" s="6">
+      <c r="D170" s="2">
         <v>174.8</v>
       </c>
       <c r="E170" s="2" t="s">
@@ -5579,7 +5577,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D171" s="6">
+      <c r="D171" s="2">
         <v>50</v>
       </c>
       <c r="E171" s="2" t="s">
@@ -5603,7 +5601,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D172" s="6">
+      <c r="D172" s="2">
         <v>60</v>
       </c>
       <c r="E172" s="2" t="s">
@@ -5627,7 +5625,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D173" s="6">
+      <c r="D173" s="2">
         <v>100</v>
       </c>
       <c r="E173" s="2" t="s">
@@ -5651,7 +5649,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D174" s="6">
+      <c r="D174" s="2">
         <v>80</v>
       </c>
       <c r="E174" s="2" t="s">
@@ -5675,7 +5673,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D175" s="6">
+      <c r="D175" s="2">
         <v>20</v>
       </c>
       <c r="E175" s="2" t="s">
@@ -5699,7 +5697,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D176" s="6">
+      <c r="D176" s="2">
         <v>55</v>
       </c>
       <c r="E176" s="2" t="s">
@@ -5723,7 +5721,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D177" s="6">
+      <c r="D177" s="2">
         <v>20</v>
       </c>
       <c r="E177" s="2" t="s">
@@ -5747,7 +5745,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D178" s="6">
+      <c r="D178" s="2">
         <v>20</v>
       </c>
       <c r="E178" s="2" t="s">
@@ -5771,7 +5769,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D179" s="6">
+      <c r="D179" s="2">
         <v>41</v>
       </c>
       <c r="E179" s="2" t="s">
@@ -5795,7 +5793,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D180" s="6">
+      <c r="D180" s="2">
         <v>25</v>
       </c>
       <c r="E180" s="2" t="s">
@@ -5819,7 +5817,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D181" s="6">
+      <c r="D181" s="2">
         <v>65</v>
       </c>
       <c r="E181" s="2" t="s">
@@ -5843,7 +5841,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D182" s="6">
+      <c r="D182" s="2">
         <v>50</v>
       </c>
       <c r="E182" s="2" t="s">
@@ -5867,7 +5865,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D183" s="6">
+      <c r="D183" s="2">
         <v>75</v>
       </c>
       <c r="E183" s="2" t="s">
@@ -5891,7 +5889,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D184" s="6">
+      <c r="D184" s="2">
         <v>150</v>
       </c>
       <c r="E184" s="2" t="s">
@@ -5915,7 +5913,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D185" s="6">
+      <c r="D185" s="2">
         <v>150</v>
       </c>
       <c r="E185" s="2" t="s">
@@ -5939,7 +5937,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D186" s="6">
+      <c r="D186" s="2">
         <v>200</v>
       </c>
       <c r="E186" s="2" t="s">
@@ -5963,7 +5961,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D187" s="6">
+      <c r="D187" s="2">
         <v>50</v>
       </c>
       <c r="E187" s="2" t="s">
@@ -5987,7 +5985,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D188" s="6">
+      <c r="D188" s="2">
         <v>46.8</v>
       </c>
       <c r="E188" s="2" t="s">
@@ -6011,7 +6009,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D189" s="6">
+      <c r="D189" s="2">
         <v>150</v>
       </c>
       <c r="E189" s="2" t="s">
@@ -6035,7 +6033,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D190" s="6">
+      <c r="D190" s="2">
         <v>150</v>
       </c>
       <c r="E190" s="2" t="s">
@@ -6059,7 +6057,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D191" s="6">
+      <c r="D191" s="2">
         <v>75</v>
       </c>
       <c r="E191" s="2" t="s">
@@ -6083,7 +6081,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D192" s="6">
+      <c r="D192" s="2">
         <v>20</v>
       </c>
       <c r="E192" s="2" t="s">
@@ -6107,7 +6105,7 @@
         <f t="shared" si="2"/>
         <v>1E-3</v>
       </c>
-      <c r="D193" s="6">
+      <c r="D193" s="2">
         <v>200</v>
       </c>
       <c r="E193" s="2" t="s">
@@ -6179,7 +6177,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D196" s="6">
+      <c r="D196" s="2">
         <v>127</v>
       </c>
       <c r="E196" s="2" t="s">
@@ -6203,7 +6201,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D197" s="6">
+      <c r="D197" s="2">
         <v>53</v>
       </c>
       <c r="E197" s="2" t="s">
@@ -6227,7 +6225,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D198" s="6">
+      <c r="D198" s="2">
         <v>60</v>
       </c>
       <c r="E198" s="2" t="s">
@@ -6251,7 +6249,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D199" s="6">
+      <c r="D199" s="2">
         <v>569</v>
       </c>
       <c r="E199" s="2" t="s">
@@ -6275,7 +6273,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D200" s="6">
+      <c r="D200" s="2">
         <v>75</v>
       </c>
       <c r="E200" s="2" t="s">
@@ -6299,7 +6297,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D201" s="6">
+      <c r="D201" s="2">
         <v>122</v>
       </c>
       <c r="E201" s="2" t="s">
@@ -6323,7 +6321,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D202" s="6">
+      <c r="D202" s="2">
         <v>314</v>
       </c>
       <c r="E202" s="2" t="s">
@@ -6347,7 +6345,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D203" s="6">
+      <c r="D203" s="2">
         <v>74.5</v>
       </c>
       <c r="E203" s="2" t="s">
@@ -6371,7 +6369,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D204" s="6">
+      <c r="D204" s="2">
         <v>20</v>
       </c>
       <c r="E204" s="2" t="s">
@@ -6395,7 +6393,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D205" s="6">
+      <c r="D205" s="2">
         <v>70</v>
       </c>
       <c r="E205" s="2" t="s">
@@ -6419,7 +6417,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D206" s="6">
+      <c r="D206" s="2">
         <v>127.86</v>
       </c>
       <c r="E206" s="2" t="s">
@@ -6443,7 +6441,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D207" s="6">
+      <c r="D207" s="2">
         <v>130</v>
       </c>
       <c r="E207" s="2" t="s">
@@ -6491,7 +6489,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D209" s="6">
+      <c r="D209" s="2">
         <v>150</v>
       </c>
       <c r="E209" s="2" t="s">
@@ -6515,7 +6513,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D210" s="6">
+      <c r="D210" s="2">
         <v>82.5</v>
       </c>
       <c r="E210" s="2" t="s">
@@ -6539,7 +6537,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D211" s="6">
+      <c r="D211" s="2">
         <v>18</v>
       </c>
       <c r="E211" s="2" t="s">
@@ -6563,7 +6561,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D212" s="6">
+      <c r="D212" s="2">
         <v>75</v>
       </c>
       <c r="E212" s="2" t="s">
@@ -6587,7 +6585,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D213" s="6">
+      <c r="D213" s="2">
         <v>150</v>
       </c>
       <c r="E213" s="2" t="s">
@@ -6611,7 +6609,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D214" s="6">
+      <c r="D214" s="2">
         <v>90</v>
       </c>
       <c r="E214" s="2" t="s">
@@ -6635,7 +6633,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D215" s="6">
+      <c r="D215" s="2">
         <v>36</v>
       </c>
       <c r="E215" s="2" t="s">
@@ -6659,7 +6657,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D216" s="6">
+      <c r="D216" s="2">
         <v>80</v>
       </c>
       <c r="E216" s="2" t="s">
@@ -6683,7 +6681,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D217" s="6">
+      <c r="D217" s="2">
         <v>500</v>
       </c>
       <c r="E217" s="2" t="s">
@@ -6707,7 +6705,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D218" s="6">
+      <c r="D218" s="2">
         <v>72</v>
       </c>
       <c r="E218" s="2" t="s">
@@ -6731,7 +6729,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D219" s="6">
+      <c r="D219" s="2">
         <v>54</v>
       </c>
       <c r="E219" s="2" t="s">
@@ -6755,7 +6753,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D220" s="6">
+      <c r="D220" s="2">
         <v>100</v>
       </c>
       <c r="E220" s="2" t="s">
@@ -6779,7 +6777,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D221" s="6">
+      <c r="D221" s="2">
         <v>100</v>
       </c>
       <c r="E221" s="2" t="s">
@@ -6803,7 +6801,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D222" s="6">
+      <c r="D222" s="2">
         <v>30</v>
       </c>
       <c r="E222" s="2" t="s">
@@ -6827,7 +6825,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D223" s="6">
+      <c r="D223" s="2">
         <v>70</v>
       </c>
       <c r="E223" s="2" t="s">
@@ -6851,7 +6849,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D224" s="6">
+      <c r="D224" s="2">
         <v>63</v>
       </c>
       <c r="E224" s="2" t="s">
@@ -6875,7 +6873,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D225" s="6">
+      <c r="D225" s="2">
         <v>94</v>
       </c>
       <c r="E225" s="2" t="s">
@@ -6899,7 +6897,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D226" s="6">
+      <c r="D226" s="2">
         <v>150</v>
       </c>
       <c r="E226" s="2" t="s">
@@ -6923,7 +6921,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D227" s="6">
+      <c r="D227" s="2">
         <v>117</v>
       </c>
       <c r="E227" s="2" t="s">
@@ -6947,7 +6945,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D228" s="6">
+      <c r="D228" s="2">
         <v>20</v>
       </c>
       <c r="E228" s="2" t="s">
@@ -6971,7 +6969,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D229" s="6">
+      <c r="D229" s="2">
         <v>90</v>
       </c>
       <c r="E229" s="2" t="s">
@@ -6995,7 +6993,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D230" s="6">
+      <c r="D230" s="2">
         <v>107</v>
       </c>
       <c r="E230" s="2" t="s">
@@ -7019,7 +7017,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D231" s="6">
+      <c r="D231" s="2">
         <v>118.56</v>
       </c>
       <c r="E231" s="2" t="s">
@@ -7043,7 +7041,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D232" s="6">
+      <c r="D232" s="2">
         <v>75</v>
       </c>
       <c r="E232" s="2" t="s">
@@ -7067,7 +7065,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D233" s="6">
+      <c r="D233" s="2">
         <v>75</v>
       </c>
       <c r="E233" s="2" t="s">
@@ -7091,7 +7089,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D234" s="6">
+      <c r="D234" s="2">
         <v>26</v>
       </c>
       <c r="E234" s="2" t="s">
@@ -7115,7 +7113,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D235" s="6">
+      <c r="D235" s="2">
         <v>26</v>
       </c>
       <c r="E235" s="2" t="s">
@@ -7139,7 +7137,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D236" s="6">
+      <c r="D236" s="2">
         <v>90</v>
       </c>
       <c r="E236" s="2" t="s">
@@ -7163,7 +7161,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D237" s="6">
+      <c r="D237" s="2">
         <v>150</v>
       </c>
       <c r="E237" s="2" t="s">
@@ -7187,7 +7185,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D238" s="6">
+      <c r="D238" s="2">
         <v>20</v>
       </c>
       <c r="E238" s="2" t="s">
@@ -7211,7 +7209,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D239" s="6">
+      <c r="D239" s="2">
         <v>15</v>
       </c>
       <c r="E239" s="2" t="s">
@@ -7235,7 +7233,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D240" s="6">
+      <c r="D240" s="2">
         <v>15</v>
       </c>
       <c r="E240" s="2" t="s">
@@ -7259,7 +7257,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D241" s="6">
+      <c r="D241" s="2">
         <v>15</v>
       </c>
       <c r="E241" s="2" t="s">
@@ -7283,7 +7281,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D242" s="6">
+      <c r="D242" s="2">
         <v>10</v>
       </c>
       <c r="E242" s="2" t="s">
@@ -7307,7 +7305,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D243" s="6">
+      <c r="D243" s="2">
         <v>150</v>
       </c>
       <c r="E243" s="2" t="s">
@@ -7355,7 +7353,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D245" s="6">
+      <c r="D245" s="2">
         <v>80</v>
       </c>
       <c r="E245" s="2" t="s">
@@ -7379,7 +7377,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D246" s="6">
+      <c r="D246" s="2">
         <v>20</v>
       </c>
       <c r="E246" s="2" t="s">
@@ -7403,7 +7401,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D247" s="6">
+      <c r="D247" s="2">
         <v>60</v>
       </c>
       <c r="E247" s="2" t="s">
@@ -7427,7 +7425,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D248" s="6">
+      <c r="D248" s="2">
         <v>102</v>
       </c>
       <c r="E248" s="2" t="s">
@@ -7451,7 +7449,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D249" s="6">
+      <c r="D249" s="2">
         <v>75</v>
       </c>
       <c r="E249" s="2" t="s">
@@ -7475,7 +7473,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D250" s="6">
+      <c r="D250" s="2">
         <v>50</v>
       </c>
       <c r="E250" s="2" t="s">
@@ -7499,7 +7497,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D251" s="6">
+      <c r="D251" s="2">
         <v>150</v>
       </c>
       <c r="E251" s="2" t="s">
@@ -7523,7 +7521,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D252" s="6">
+      <c r="D252" s="2">
         <v>75</v>
       </c>
       <c r="E252" s="2" t="s">
@@ -7547,7 +7545,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D253" s="6">
+      <c r="D253" s="2">
         <v>62</v>
       </c>
       <c r="E253" s="2" t="s">
@@ -7571,7 +7569,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D254" s="6">
+      <c r="D254" s="2">
         <v>60</v>
       </c>
       <c r="E254" s="2" t="s">
@@ -7595,7 +7593,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D255" s="6">
+      <c r="D255" s="2">
         <v>100</v>
       </c>
       <c r="E255" s="2" t="s">
@@ -7619,7 +7617,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D256" s="6">
+      <c r="D256" s="2">
         <v>100</v>
       </c>
       <c r="E256" s="2" t="s">
@@ -7643,7 +7641,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D257" s="6">
+      <c r="D257" s="2">
         <v>20</v>
       </c>
       <c r="E257" s="2" t="s">
@@ -7667,7 +7665,7 @@
         <f t="shared" si="3"/>
         <v>1E-3</v>
       </c>
-      <c r="D258" s="6">
+      <c r="D258" s="2">
         <v>62.5</v>
       </c>
       <c r="E258" s="2" t="s">
@@ -7691,7 +7689,7 @@
         <f t="shared" ref="C259:C312" si="4">1/1000</f>
         <v>1E-3</v>
       </c>
-      <c r="D259" s="6">
+      <c r="D259" s="2">
         <v>14.2</v>
       </c>
       <c r="E259" s="2" t="s">
@@ -7715,7 +7713,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D260" s="6">
+      <c r="D260" s="2">
         <v>128</v>
       </c>
       <c r="E260" s="2" t="s">
@@ -7739,7 +7737,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D261" s="6">
+      <c r="D261" s="2">
         <v>160</v>
       </c>
       <c r="E261" s="2" t="s">
@@ -7763,7 +7761,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D262" s="6">
+      <c r="D262" s="2">
         <v>20</v>
       </c>
       <c r="E262" s="2" t="s">
@@ -7787,7 +7785,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D263" s="6">
+      <c r="D263" s="2">
         <v>150</v>
       </c>
       <c r="E263" s="2" t="s">
@@ -7811,7 +7809,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D264" s="6">
+      <c r="D264" s="2">
         <v>150</v>
       </c>
       <c r="E264" s="2" t="s">
@@ -7835,7 +7833,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D265" s="6">
+      <c r="D265" s="2">
         <v>500</v>
       </c>
       <c r="E265" s="2" t="s">
@@ -7859,7 +7857,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D266" s="6">
+      <c r="D266" s="2">
         <v>50</v>
       </c>
       <c r="E266" s="2" t="s">
@@ -7931,7 +7929,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D269" s="6">
+      <c r="D269" s="2">
         <v>127.5</v>
       </c>
       <c r="E269" s="2" t="s">
@@ -7955,7 +7953,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D270" s="6">
+      <c r="D270" s="2">
         <v>100</v>
       </c>
       <c r="E270" s="2" t="s">
@@ -7979,7 +7977,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D271" s="6">
+      <c r="D271" s="2">
         <v>100</v>
       </c>
       <c r="E271" s="2" t="s">
@@ -8003,7 +8001,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D272" s="6">
+      <c r="D272" s="2">
         <v>833</v>
       </c>
       <c r="E272" s="2" t="s">
@@ -8027,7 +8025,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D273" s="6">
+      <c r="D273" s="2">
         <v>836</v>
       </c>
       <c r="E273" s="2" t="s">
@@ -8051,7 +8049,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D274" s="6">
+      <c r="D274" s="2">
         <v>820</v>
       </c>
       <c r="E274" s="2" t="s">
@@ -8075,7 +8073,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D275" s="6">
+      <c r="D275" s="2">
         <v>800.1</v>
       </c>
       <c r="E275" s="2" t="s">
@@ -8099,7 +8097,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D276" s="6">
+      <c r="D276" s="2">
         <v>800.1</v>
       </c>
       <c r="E276" s="2" t="s">
@@ -8123,7 +8121,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D277" s="6">
+      <c r="D277" s="2">
         <v>75</v>
       </c>
       <c r="E277" s="2" t="s">
@@ -8147,7 +8145,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D278" s="6">
+      <c r="D278" s="2">
         <v>79</v>
       </c>
       <c r="E278" s="2" t="s">
@@ -8175,7 +8173,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D279" s="6">
+      <c r="D279" s="2">
         <v>260</v>
       </c>
       <c r="E279" s="2" t="s">
@@ -8186,6 +8184,10 @@
       </c>
       <c r="G279" s="2" t="s">
         <v>336</v>
+      </c>
+      <c r="H279">
+        <f>100-(3000/H278)</f>
+        <v>99.926440244836286</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.35">
@@ -8199,7 +8201,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D280" s="6">
+      <c r="D280" s="2">
         <v>90</v>
       </c>
       <c r="E280" s="2" t="s">
@@ -8223,7 +8225,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D281" s="6">
+      <c r="D281" s="2">
         <v>250</v>
       </c>
       <c r="E281" s="2" t="s">
@@ -8247,7 +8249,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D282" s="6">
+      <c r="D282" s="2">
         <v>167</v>
       </c>
       <c r="E282" s="2" t="s">
@@ -8258,6 +8260,10 @@
       </c>
       <c r="G282" s="2" t="s">
         <v>336</v>
+      </c>
+      <c r="H282" s="5">
+        <f>(3/41)</f>
+        <v>7.3170731707317069E-2</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.35">
@@ -8271,7 +8277,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D283" s="6">
+      <c r="D283" s="2">
         <v>20</v>
       </c>
       <c r="E283" s="2" t="s">
@@ -8295,7 +8301,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D284" s="6">
+      <c r="D284" s="2">
         <v>20</v>
       </c>
       <c r="E284" s="2" t="s">
@@ -8319,7 +8325,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D285" s="6">
+      <c r="D285" s="2">
         <v>20</v>
       </c>
       <c r="E285" s="2" t="s">
@@ -8343,7 +8349,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D286" s="6">
+      <c r="D286" s="2">
         <v>125</v>
       </c>
       <c r="E286" s="2" t="s">
@@ -8391,7 +8397,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D288" s="6">
+      <c r="D288" s="2">
         <v>150</v>
       </c>
       <c r="E288" s="2" t="s">
@@ -8415,7 +8421,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D289" s="6">
+      <c r="D289" s="2">
         <v>20</v>
       </c>
       <c r="E289" s="2" t="s">
@@ -8439,7 +8445,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D290" s="6">
+      <c r="D290" s="2">
         <v>80</v>
       </c>
       <c r="E290" s="2" t="s">
@@ -8463,7 +8469,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D291" s="6">
+      <c r="D291" s="2">
         <v>188.5</v>
       </c>
       <c r="E291" s="2" t="s">
@@ -8487,7 +8493,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D292" s="6">
+      <c r="D292" s="2">
         <v>45</v>
       </c>
       <c r="E292" s="2" t="s">
@@ -8511,7 +8517,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D293" s="6">
+      <c r="D293" s="2">
         <v>55</v>
       </c>
       <c r="E293" s="2" t="s">
@@ -8535,7 +8541,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D294" s="6">
+      <c r="D294" s="2">
         <v>50</v>
       </c>
       <c r="E294" s="2" t="s">
@@ -8559,7 +8565,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D295" s="6">
+      <c r="D295" s="2">
         <v>200</v>
       </c>
       <c r="E295" s="2" t="s">
@@ -8583,7 +8589,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D296" s="6">
+      <c r="D296" s="2">
         <v>106</v>
       </c>
       <c r="E296" s="2" t="s">
@@ -8607,7 +8613,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D297" s="6">
+      <c r="D297" s="2">
         <v>65</v>
       </c>
       <c r="E297" s="2" t="s">
@@ -8631,7 +8637,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D298" s="6">
+      <c r="D298" s="2">
         <v>90</v>
       </c>
       <c r="E298" s="2" t="s">
@@ -8655,7 +8661,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D299" s="6">
+      <c r="D299" s="2">
         <v>100</v>
       </c>
       <c r="E299" s="2" t="s">
@@ -8679,7 +8685,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D300" s="6">
+      <c r="D300" s="2">
         <v>250</v>
       </c>
       <c r="E300" s="2" t="s">
@@ -8703,7 +8709,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D301" s="6">
+      <c r="D301" s="2">
         <v>225</v>
       </c>
       <c r="E301" s="2" t="s">
@@ -8727,7 +8733,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D302" s="6">
+      <c r="D302" s="2">
         <v>222</v>
       </c>
       <c r="E302" s="2" t="s">
@@ -8751,7 +8757,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D303" s="6">
+      <c r="D303" s="2">
         <v>150</v>
       </c>
       <c r="E303" s="2" t="s">
@@ -8775,7 +8781,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D304" s="6">
+      <c r="D304" s="2">
         <v>50</v>
       </c>
       <c r="E304" s="2" t="s">
@@ -8799,7 +8805,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D305" s="6">
+      <c r="D305" s="2">
         <v>120</v>
       </c>
       <c r="E305" s="2" t="s">
@@ -8823,7 +8829,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D306" s="6">
+      <c r="D306" s="2">
         <v>82</v>
       </c>
       <c r="E306" s="2" t="s">
@@ -8847,7 +8853,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D307" s="6">
+      <c r="D307" s="2">
         <v>70</v>
       </c>
       <c r="E307" s="2" t="s">
@@ -8871,7 +8877,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D308" s="6">
+      <c r="D308" s="2">
         <v>57</v>
       </c>
       <c r="E308" s="2" t="s">
@@ -8895,7 +8901,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D309" s="6">
+      <c r="D309" s="2">
         <v>22</v>
       </c>
       <c r="E309" s="2" t="s">
@@ -8919,7 +8925,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D310" s="6">
+      <c r="D310" s="2">
         <v>98</v>
       </c>
       <c r="E310" s="2" t="s">
@@ -8943,7 +8949,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D311" s="6">
+      <c r="D311" s="2">
         <v>64.2</v>
       </c>
       <c r="E311" s="2" t="s">
@@ -8967,7 +8973,7 @@
         <f t="shared" si="4"/>
         <v>1E-3</v>
       </c>
-      <c r="D312" s="6">
+      <c r="D312" s="2">
         <v>120</v>
       </c>
       <c r="E312" s="2" t="s">
